--- a/output/yearly_surface_area_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_47_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449764150212</v>
+        <v>10.84497638245558</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907223044558</v>
+        <v>37.78907211697146</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.431028299893355</v>
+        <v>6.040693624230625</v>
       </c>
       <c r="C2" t="n">
-        <v>11.45208697003904</v>
+        <v>5.837471849451535</v>
       </c>
       <c r="D2" t="n">
-        <v>23.778911144562</v>
+        <v>23.25171262738146</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.70229376590174</v>
+        <v>19.14898897133403</v>
       </c>
       <c r="C3" t="n">
-        <v>34.01264921363074</v>
+        <v>37.65002445786518</v>
       </c>
       <c r="D3" t="n">
-        <v>65.21259125459437</v>
+        <v>69.69426952448107</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.15227837181205</v>
+        <v>38.21158414469435</v>
       </c>
       <c r="C4" t="n">
-        <v>65.12816095202915</v>
+        <v>80.12435713439919</v>
       </c>
       <c r="D4" t="n">
-        <v>89.76021085158163</v>
+        <v>78.24823727158353</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.32590884674349</v>
+        <v>47.14843349645307</v>
       </c>
       <c r="C5" t="n">
-        <v>81.16599144860506</v>
+        <v>106.9859560702962</v>
       </c>
       <c r="D5" t="n">
-        <v>64.20629985774141</v>
+        <v>54.53608497091033</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.64788103600744</v>
+        <v>46.57116584635595</v>
       </c>
       <c r="C6" t="n">
-        <v>93.18258334858602</v>
+        <v>143.4166498794868</v>
       </c>
       <c r="D6" t="n">
-        <v>44.43782808502763</v>
+        <v>40.69442408873454</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.99078872223005</v>
+        <v>32.87774886752143</v>
       </c>
       <c r="C7" t="n">
-        <v>91.80617306723197</v>
+        <v>154.1481340346087</v>
       </c>
       <c r="D7" t="n">
-        <v>38.44720359371359</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.85246010692249</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C8" t="n">
-        <v>71.26506585127596</v>
+        <v>108.5665698741335</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>35.549084370777</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>44.5968712131156</v>
+        <v>57.02187015806322</v>
       </c>
       <c r="D9" t="n">
-        <v>34.27968458918587</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>28.20561154301086</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.708670512642043</v>
+        <v>7.65105218841891</v>
       </c>
       <c r="C21" t="n">
-        <v>95.3947975939453</v>
+        <v>92.76900778457927</v>
       </c>
       <c r="D21" t="n">
-        <v>8.672254326722298</v>
+        <v>7.65105218841891</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.004368959173493</v>
+        <v>7.750898125028567</v>
       </c>
       <c r="C2" t="n">
-        <v>8.542186774651496</v>
+        <v>15.63335044242621</v>
       </c>
       <c r="D2" t="n">
-        <v>22.13644723535708</v>
+        <v>20.11110172149591</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.4224956701914</v>
+        <v>19.45333075965055</v>
       </c>
       <c r="C3" t="n">
-        <v>39.35826546325463</v>
+        <v>30.00220984178253</v>
       </c>
       <c r="D3" t="n">
-        <v>68.1283819362074</v>
+        <v>71.07853378746907</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.4886169237412</v>
+        <v>36.82044764777662</v>
       </c>
       <c r="C4" t="n">
-        <v>74.54704842657306</v>
+        <v>86.63334441355555</v>
       </c>
       <c r="D4" t="n">
-        <v>99.19186104628074</v>
+        <v>90.9216183857056</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.5291716792516</v>
+        <v>51.86082247683777</v>
       </c>
       <c r="C5" t="n">
-        <v>100.6291396852981</v>
+        <v>124.5101525911018</v>
       </c>
       <c r="D5" t="n">
-        <v>79.93880681829654</v>
+        <v>67.59332943739291</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.1875234781737</v>
+        <v>53.93721887131977</v>
       </c>
       <c r="C6" t="n">
-        <v>109.726013912849</v>
+        <v>154.4858552448696</v>
       </c>
       <c r="D6" t="n">
-        <v>52.72966919509619</v>
+        <v>46.77242412572655</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.35117224514665</v>
+        <v>42.75903951076558</v>
       </c>
       <c r="C7" t="n">
-        <v>113.3054660425329</v>
+        <v>179.5999432672072</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>40.36357511240336</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.5283444958008</v>
+        <v>24.70077223884975</v>
       </c>
       <c r="C8" t="n">
-        <v>95.46514676095984</v>
+        <v>151.1253328532327</v>
       </c>
       <c r="D8" t="n">
-        <v>38.46978379091126</v>
+        <v>37.05115835827462</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.42812411450962</v>
+        <v>11.6484365108884</v>
       </c>
       <c r="C9" t="n">
-        <v>66.11874438561416</v>
+        <v>92.07811718130831</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>41.85190463204153</v>
+        <v>48.11545498513618</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.8092064546734</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
         <v>34.93156506480576</v>
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>28.87810872041993</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.11939767148639</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.895293256248565</v>
+        <v>7.822204086935276</v>
       </c>
       <c r="C21" t="n">
-        <v>104.6126356452935</v>
+        <v>100.7108776192917</v>
       </c>
       <c r="D21" t="n">
-        <v>9.869116570310707</v>
+        <v>8.799979597802185</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.260425183532663</v>
+        <v>7.976700097005335</v>
       </c>
       <c r="C2" t="n">
-        <v>9.982410656781568</v>
+        <v>15.56168286001619</v>
       </c>
       <c r="D2" t="n">
-        <v>24.90006702281185</v>
+        <v>26.05852931382309</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.93791321492097</v>
+        <v>21.76534660315179</v>
       </c>
       <c r="C3" t="n">
-        <v>36.08413686959152</v>
+        <v>43.30489123432681</v>
       </c>
       <c r="D3" t="n">
-        <v>69.10522090193298</v>
+        <v>70.06242491357362</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.18681946790993</v>
+        <v>35.90153179660161</v>
       </c>
       <c r="C4" t="n">
-        <v>84.80827543136071</v>
+        <v>80.43066241812419</v>
       </c>
       <c r="D4" t="n">
-        <v>108.1385278750819</v>
+        <v>101.6678287563912</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.54175447295756</v>
+        <v>52.71985171805373</v>
       </c>
       <c r="C5" t="n">
-        <v>117.3924817353124</v>
+        <v>137.6901155206152</v>
       </c>
       <c r="D5" t="n">
-        <v>92.67698328089891</v>
+        <v>79.30067081053612</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.27810630887167</v>
+        <v>60.09572222006002</v>
       </c>
       <c r="C6" t="n">
-        <v>130.978888214384</v>
+        <v>172.7198553558456</v>
       </c>
       <c r="D6" t="n">
-        <v>62.792583163626</v>
+        <v>54.74225198880216</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.8132566186774</v>
+        <v>51.68214439466484</v>
       </c>
       <c r="C7" t="n">
-        <v>134.2657795282023</v>
+        <v>196.9670601553333</v>
       </c>
       <c r="D7" t="n">
-        <v>47.19064864773568</v>
+        <v>43.23813239043802</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.53940576245478</v>
+        <v>32.96217917008666</v>
       </c>
       <c r="C8" t="n">
-        <v>119.4983305609218</v>
+        <v>186.4240715594268</v>
       </c>
       <c r="D8" t="n">
-        <v>40.47254910757476</v>
+        <v>38.7201294554942</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.8656237377052</v>
+        <v>16.64062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>89.1937424262312</v>
+        <v>130.57342641253</v>
       </c>
       <c r="D9" t="n">
-        <v>37.71874679716245</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.971791358484101</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>58.2225476003571</v>
+        <v>72.74259614616741</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>39.80397892098267</v>
+        <v>41.75863860013807</v>
       </c>
       <c r="D11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.82120841130262</v>
+        <v>33.30088212805181</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>28.5776939229204</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.066463795672735</v>
+        <v>7.976936949783986</v>
       </c>
       <c r="C21" t="n">
-        <v>112.9304931394183</v>
+        <v>107.6886488220838</v>
       </c>
       <c r="D21" t="n">
-        <v>11.09138771905001</v>
+        <v>9.971171187229983</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.392560212978482</v>
+        <v>7.390596717569988</v>
       </c>
       <c r="C2" t="n">
-        <v>6.707300315414209</v>
+        <v>10.83064067325081</v>
       </c>
       <c r="D2" t="n">
-        <v>20.2514916432032</v>
+        <v>21.51892792938584</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.79265561242145</v>
+        <v>25.2996383384403</v>
       </c>
       <c r="C3" t="n">
-        <v>53.86358779350125</v>
+        <v>63.02820261264523</v>
       </c>
       <c r="D3" t="n">
-        <v>77.05737730633216</v>
+        <v>75.90873249236338</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.75967710110456</v>
+        <v>25.32123678793373</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6325268967673</v>
+        <v>111.201580712332</v>
       </c>
       <c r="D4" t="n">
-        <v>104.4756271905371</v>
+        <v>94.86529891366503</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.25041208450773</v>
+        <v>33.84575210390879</v>
       </c>
       <c r="C5" t="n">
-        <v>78.2452920284708</v>
+        <v>103.206227408946</v>
       </c>
       <c r="D5" t="n">
-        <v>63.32272692391928</v>
+        <v>54.02066742618075</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.41766904712818</v>
+        <v>32.08056973167303</v>
       </c>
       <c r="C6" t="n">
-        <v>88.43288795543995</v>
+        <v>129.7310868822863</v>
       </c>
       <c r="D6" t="n">
-        <v>31.07427833482005</v>
+        <v>28.45792070300229</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.92416874706152</v>
+        <v>21.79872602509618</v>
       </c>
       <c r="C7" t="n">
-        <v>84.02091377255476</v>
+        <v>131.0917892003723</v>
       </c>
       <c r="D7" t="n">
-        <v>28.44613973055133</v>
+        <v>27.18852092141116</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.2641722479004</v>
+        <v>11.51590057081509</v>
       </c>
       <c r="C8" t="n">
-        <v>65.67401267559038</v>
+        <v>96.21618375470864</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>44.37499623195582</v>
+        <v>55.46874528994476</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>32.74128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.37368602241954</v>
+        <v>4.518002934943821</v>
       </c>
       <c r="C2" t="n">
-        <v>3.536255230697011</v>
+        <v>4.631885668636452</v>
       </c>
       <c r="D2" t="n">
-        <v>14.47292465600648</v>
+        <v>15.60193451589031</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.2996383384403</v>
+        <v>25.96722677732814</v>
       </c>
       <c r="C3" t="n">
-        <v>40.59035883208438</v>
+        <v>53.72614311490671</v>
       </c>
       <c r="D3" t="n">
-        <v>75.90873249236338</v>
+        <v>75.71238295151402</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.05093737409637</v>
+        <v>34.88051418418493</v>
       </c>
       <c r="C4" t="n">
-        <v>123.198537658228</v>
+        <v>136.9184618250772</v>
       </c>
       <c r="D4" t="n">
-        <v>118.0296359953685</v>
+        <v>108.5596976402038</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.1528592088888</v>
+        <v>37.45367491701582</v>
       </c>
       <c r="C5" t="n">
-        <v>133.9349305518711</v>
+        <v>149.5447190493954</v>
       </c>
       <c r="D5" t="n">
-        <v>79.76700097005336</v>
+        <v>68.20692175254716</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>37.55479493055324</v>
       </c>
       <c r="C6" t="n">
-        <v>107.1096562810313</v>
+        <v>149.2933916371082</v>
       </c>
       <c r="D6" t="n">
-        <v>38.56108632740622</v>
+        <v>34.13340418125311</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.96598298771663</v>
+        <v>20.18178755620168</v>
       </c>
       <c r="C7" t="n">
-        <v>104.8614540383061</v>
+        <v>158.3401967317426</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>29.46421209985527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>9.429686699290613</v>
       </c>
       <c r="C8" t="n">
-        <v>84.70028318389356</v>
+        <v>122.9197213102219</v>
       </c>
       <c r="D8" t="n">
-        <v>28.87319998189869</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>50.25468323268996</v>
+        <v>59.46249495082079</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
         <v>33.88011327355743</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>30.38607319414302</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.52782041198629</v>
+        <v>4.303981935418017</v>
       </c>
       <c r="C2" t="n">
-        <v>13.45877927751952</v>
+        <v>13.00619358586174</v>
       </c>
       <c r="D2" t="n">
-        <v>18.22025564311655</v>
+        <v>22.67739022039708</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.19945901487813</v>
+        <v>20.68051538995906</v>
       </c>
       <c r="C3" t="n">
-        <v>26.19793748782614</v>
+        <v>35.56381058634071</v>
       </c>
       <c r="D3" t="n">
-        <v>70.17532589956201</v>
+        <v>70.93618037035328</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.94280625790898</v>
+        <v>41.7213321873767</v>
       </c>
       <c r="C4" t="n">
-        <v>111.814191279782</v>
+        <v>135.3614099661417</v>
       </c>
       <c r="D4" t="n">
-        <v>128.1377103582937</v>
+        <v>119.6632641752352</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.34416114249668</v>
+        <v>43.98229715025711</v>
       </c>
       <c r="C5" t="n">
-        <v>180.5679465035946</v>
+        <v>197.7485313279138</v>
       </c>
       <c r="D5" t="n">
-        <v>101.3654504634832</v>
+        <v>87.71915737445252</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.45920555034281</v>
+        <v>43.23027840880406</v>
       </c>
       <c r="C6" t="n">
-        <v>158.9135373910227</v>
+        <v>190.7928488433252</v>
       </c>
       <c r="D6" t="n">
-        <v>52.20639766873265</v>
+        <v>44.84034464376883</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.12863431145211</v>
+        <v>29.58398531977338</v>
       </c>
       <c r="C7" t="n">
-        <v>129.8341703912322</v>
+        <v>184.5106452838498</v>
       </c>
       <c r="D7" t="n">
-        <v>34.61446055633404</v>
+        <v>32.03933632809466</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>13.68556299720053</v>
       </c>
       <c r="C8" t="n">
-        <v>110.736232300519</v>
+        <v>162.3074392046039</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>29.2069942013426</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.101561981893925</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>74.54999366968578</v>
+        <v>98.29061665378212</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>47.83074815090461</v>
       </c>
       <c r="D10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>34.65078522139116</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>26.68684784454105</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>35.50686921949439</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.68704346652352</v>
+        <v>2.623229865747478</v>
       </c>
       <c r="C2" t="n">
-        <v>6.165375582669969</v>
+        <v>6.286130550292327</v>
       </c>
       <c r="D2" t="n">
-        <v>12.58306032533137</v>
+        <v>15.81301027230337</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.0521968592411</v>
+        <v>20.15037162966578</v>
       </c>
       <c r="C3" t="n">
-        <v>39.49571014184918</v>
+        <v>44.02156705842698</v>
       </c>
       <c r="D3" t="n">
-        <v>70.83309686140737</v>
+        <v>73.75870502006286</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.30765655099029</v>
+        <v>45.69053815564656</v>
       </c>
       <c r="C4" t="n">
-        <v>105.5349329634194</v>
+        <v>132.3621707296677</v>
       </c>
       <c r="D4" t="n">
-        <v>136.1016477351438</v>
+        <v>128.2398121195353</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.86587008407924</v>
+        <v>45.82307409571988</v>
       </c>
       <c r="C5" t="n">
-        <v>215.1500093856885</v>
+        <v>243.2279937271473</v>
       </c>
       <c r="D5" t="n">
-        <v>109.2194320974577</v>
+        <v>92.35791527701869</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.05290086950487</v>
+        <v>35.13969557810609</v>
       </c>
       <c r="C6" t="n">
-        <v>192.3626634224158</v>
+        <v>222.6721602956276</v>
       </c>
       <c r="D6" t="n">
-        <v>50.99884799250906</v>
+        <v>43.91455655866408</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>9.042878103817369</v>
       </c>
       <c r="C7" t="n">
-        <v>139.4759145946401</v>
+        <v>200.3805969229995</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.172427743048944</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>89.62374792069132</v>
+        <v>118.580396457451</v>
       </c>
       <c r="D8" t="n">
-        <v>32.29459073119883</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>36.49843440078366</v>
       </c>
       <c r="D9" t="n">
-        <v>32.06093477758807</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>21.32356013624072</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.7451308119901</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>30.22212132753381</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30.49799243242716</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.526437753654543</v>
+        <v>3.722787294503905</v>
       </c>
       <c r="C2" t="n">
-        <v>5.165956419746716</v>
+        <v>5.048146695237099</v>
       </c>
       <c r="D2" t="n">
-        <v>15.15523931045801</v>
+        <v>18.99485458176729</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.65258448588365</v>
+        <v>14.90783888898781</v>
       </c>
       <c r="C3" t="n">
-        <v>31.53373626040755</v>
+        <v>34.46425315758428</v>
       </c>
       <c r="D3" t="n">
-        <v>64.99169802113884</v>
+        <v>69.5960947540564</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.4615699563788</v>
+        <v>42.20631555327462</v>
       </c>
       <c r="C4" t="n">
-        <v>102.9823889323777</v>
+        <v>122.7901306132613</v>
       </c>
       <c r="D4" t="n">
-        <v>139.8028365801543</v>
+        <v>134.0979006707761</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.90424036000288</v>
+        <v>55.07604620824608</v>
       </c>
       <c r="C5" t="n">
-        <v>207.2223966738956</v>
+        <v>242.9334694158733</v>
       </c>
       <c r="D5" t="n">
-        <v>130.3515514313703</v>
+        <v>112.6310053697153</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.71958967614647</v>
+        <v>45.16235789076178</v>
       </c>
       <c r="C6" t="n">
-        <v>260.2269552261808</v>
+        <v>296.0911806100211</v>
       </c>
       <c r="D6" t="n">
-        <v>67.54227855677206</v>
+        <v>56.75483478250812</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.80439552714341</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="C7" t="n">
-        <v>201.0992362425081</v>
+        <v>250.9847823384013</v>
       </c>
       <c r="D7" t="n">
-        <v>40.18391528252619</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>129.2618114796563</v>
+        <v>175.9095536469435</v>
       </c>
       <c r="D8" t="n">
-        <v>34.04701038327938</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>62.79061966821748</v>
+        <v>74.32811868852599</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.88363935374691</v>
+        <v>32.45657910239955</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>24.6997904911455</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.82929907264807</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.60978849752428</v>
-      </c>
-      <c r="D13" t="n">
-        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.448478774391545</v>
+        <v>2.581996462169111</v>
       </c>
       <c r="C2" t="n">
-        <v>4.153774536668254</v>
+        <v>2.817615911188346</v>
       </c>
       <c r="D2" t="n">
-        <v>11.25377393378119</v>
+        <v>13.79159174925919</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.67574552015807</v>
+        <v>14.05862712481433</v>
       </c>
       <c r="C3" t="n">
-        <v>26.8557084496715</v>
+        <v>28.66212422548563</v>
       </c>
       <c r="D3" t="n">
-        <v>62.74840451693489</v>
+        <v>68.7616092054466</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.58621085708914</v>
+        <v>38.00738062221102</v>
       </c>
       <c r="C4" t="n">
-        <v>94.3420273873015</v>
+        <v>110.1678003797601</v>
       </c>
       <c r="D4" t="n">
-        <v>140.8110914724158</v>
+        <v>137.1481907878709</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.13204688511715</v>
+        <v>59.101211795658</v>
       </c>
       <c r="C5" t="n">
-        <v>207.5169209851696</v>
+        <v>244.9215085169731</v>
       </c>
       <c r="D5" t="n">
-        <v>144.8323300690107</v>
+        <v>126.6945412330509</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.05168244208915</v>
+        <v>52.04539104523617</v>
       </c>
       <c r="C6" t="n">
-        <v>295.6484123954057</v>
+        <v>337.2283729133709</v>
       </c>
       <c r="D6" t="n">
-        <v>80.66431837173494</v>
+        <v>67.01900703040852</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.94791061841269</v>
+        <v>16.64847756861741</v>
       </c>
       <c r="C7" t="n">
-        <v>260.386980101973</v>
+        <v>306.4996697704457</v>
       </c>
       <c r="D7" t="n">
-        <v>45.57371017884118</v>
+        <v>40.12402867256714</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>166.5633155025138</v>
+        <v>220.7214276072891</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>33.21252483466959</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>72.33124385808797</v>
+        <v>78.21093085882212</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>32.31422568528377</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.52209415667683</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.151410130632261</v>
+        <v>3.541163969218245</v>
       </c>
       <c r="C2" t="n">
-        <v>6.202681995431348</v>
+        <v>3.73653176236336</v>
       </c>
       <c r="D2" t="n">
-        <v>16.92631216891926</v>
+        <v>15.8051562906694</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.07902284242526</v>
+        <v>11.53553552490002</v>
       </c>
       <c r="C3" t="n">
-        <v>21.74571164906685</v>
+        <v>20.96522222419064</v>
       </c>
       <c r="D3" t="n">
-        <v>57.95256698168922</v>
+        <v>64.49100669197297</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.35349559345364</v>
+        <v>32.6087499965578</v>
       </c>
       <c r="C4" t="n">
-        <v>82.01323971737004</v>
+        <v>93.84428130124836</v>
       </c>
       <c r="D4" t="n">
-        <v>139.7390229793783</v>
+        <v>138.5648527250991</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.65942532874693</v>
+        <v>58.07037670619884</v>
       </c>
       <c r="C5" t="n">
-        <v>192.6679869584366</v>
+        <v>225.0902048911875</v>
       </c>
       <c r="D5" t="n">
-        <v>157.3496132981575</v>
+        <v>139.9235915477767</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>63.51711296936016</v>
+        <v>61.54478183152831</v>
       </c>
       <c r="C6" t="n">
-        <v>310.3000151335851</v>
+        <v>361.3391147819684</v>
       </c>
       <c r="D6" t="n">
-        <v>99.18008007382979</v>
+        <v>81.71086142446205</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.15910954801276</v>
+        <v>30.42239785920016</v>
       </c>
       <c r="C7" t="n">
-        <v>327.1006635963608</v>
+        <v>373.3331264847516</v>
       </c>
       <c r="D7" t="n">
-        <v>53.83806235319084</v>
+        <v>46.71155576806323</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>237.3276900246239</v>
+        <v>287.3133743863503</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>35.29873870619407</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>121.1437397132394</v>
+        <v>144.2187377538564</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>33.05937219280708</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
         <v>51.24723016168351</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>25.76596849795754</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>20.61179305066178</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.676064315327558</v>
+        <v>6.864379948093698</v>
       </c>
       <c r="C2" t="n">
-        <v>8.171086142446203</v>
+        <v>14.47979688993621</v>
       </c>
       <c r="D2" t="n">
-        <v>3.842560514422016</v>
+        <v>5.501714134599125</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.281581664669587</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C2" t="n">
-        <v>3.57356164345839</v>
+        <v>2.21285932537231</v>
       </c>
       <c r="D2" t="n">
-        <v>12.59287780237384</v>
+        <v>11.75839225376405</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.72621556370216</v>
+        <v>15.23181563138926</v>
       </c>
       <c r="C3" t="n">
-        <v>25.7316073283089</v>
+        <v>23.09070600388498</v>
       </c>
       <c r="D3" t="n">
-        <v>63.98540662428587</v>
+        <v>70.42567156414495</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.7078087036955</v>
+        <v>44.56741878198821</v>
       </c>
       <c r="C4" t="n">
-        <v>115.8982617294487</v>
+        <v>131.8006110428385</v>
       </c>
       <c r="D4" t="n">
-        <v>144.3846531158742</v>
+        <v>140.5303116290012</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.86462629446773</v>
+        <v>34.65569395991241</v>
       </c>
       <c r="C5" t="n">
-        <v>274.1039590257095</v>
+        <v>319.6570525027615</v>
       </c>
       <c r="D5" t="n">
-        <v>142.9179220457295</v>
+        <v>124.2892593576462</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.96482131356314</v>
+        <v>18.87802660496192</v>
       </c>
       <c r="C6" t="n">
-        <v>273.2282400735214</v>
+        <v>306.0735912668026</v>
       </c>
       <c r="D6" t="n">
-        <v>79.41651703963724</v>
+        <v>66.29447722467438</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.809001166028376</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>166.9039819558875</v>
+        <v>202.057422001853</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>30.30262463928205</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.50207398749762</v>
       </c>
       <c r="C8" t="n">
-        <v>89.2899537012474</v>
+        <v>106.3134588928871</v>
       </c>
       <c r="D8" t="n">
-        <v>24.78422079371073</v>
+        <v>24.36697801940583</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
         <v>39.04999668412111</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>19.63593583264045</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>22.91890015564179</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.64477156197868</v>
+        <v>18.79065105928395</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>16.52575910558656</v>
+        <v>14.9264920953685</v>
       </c>
       <c r="D11" t="n">
-        <v>16.52575910558656</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.0652783745658</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.626036240139976</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.8226478228966</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>24.36697801940583</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.540984042768997</v>
+        <v>7.970809610779853</v>
       </c>
       <c r="C2" t="n">
-        <v>3.579452129683871</v>
+        <v>7.740098900281853</v>
       </c>
       <c r="D2" t="n">
-        <v>16.31370160146925</v>
+        <v>7.001824626688252</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.940195505498956</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="C3" t="n">
-        <v>20.91613483897829</v>
+        <v>36.48665342833271</v>
       </c>
       <c r="D3" t="n">
-        <v>6.518804756198822</v>
+        <v>7.755806863549802</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39913824883024</v>
+        <v>13.39739370469528</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14842965564065</v>
+        <v>70.13929645399294</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576369205744734</v>
+        <v>1.576163965258268</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.37663126553228</v>
+        <v>5.218970795776044</v>
       </c>
       <c r="C2" t="n">
-        <v>3.562762418711675</v>
+        <v>5.832563110930301</v>
       </c>
       <c r="D2" t="n">
-        <v>16.93220265514474</v>
+        <v>18.88980757741288</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.45270886484479</v>
+        <v>22.3445777486574</v>
       </c>
       <c r="C3" t="n">
-        <v>16.70443718775948</v>
+        <v>32.54493639578177</v>
       </c>
       <c r="D3" t="n">
-        <v>18.64338890364693</v>
+        <v>11.76133749687679</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.65236350170539</v>
+        <v>16.8978414854961</v>
       </c>
       <c r="C4" t="n">
-        <v>32.40454647407447</v>
+        <v>56.13044324260714</v>
       </c>
       <c r="D4" t="n">
-        <v>18.48041878474196</v>
+        <v>19.13131751265759</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44354771974541</v>
+        <v>15.43804107257887</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15873991015864</v>
+        <v>86.12801861544003</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251273204156929</v>
+        <v>3.250113910016605</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.972552122010095</v>
+        <v>6.359761628110838</v>
       </c>
       <c r="C2" t="n">
-        <v>3.937790041733956</v>
+        <v>7.428884878035614</v>
       </c>
       <c r="D2" t="n">
-        <v>26.34519964346316</v>
+        <v>25.37425116396306</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.29072049364407</v>
+        <v>20.12582793705961</v>
       </c>
       <c r="C3" t="n">
-        <v>14.98146996680633</v>
+        <v>26.64954143177967</v>
       </c>
       <c r="D3" t="n">
-        <v>27.86199984652448</v>
+        <v>24.14117604742907</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.92635322664826</v>
+        <v>31.38352886165779</v>
       </c>
       <c r="C4" t="n">
-        <v>37.9690924617454</v>
+        <v>70.82033414125216</v>
       </c>
       <c r="D4" t="n">
-        <v>23.67484588791183</v>
+        <v>20.73942025221387</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.67650628368406</v>
+        <v>14.55440971545897</v>
       </c>
       <c r="C5" t="n">
-        <v>36.37375244234433</v>
+        <v>60.37748381117885</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.550605897829</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.79113408536946</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.67707142522758</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5350,7 +5350,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74053362922986</v>
+        <v>16.72493228965022</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1172551383022</v>
+        <v>102.0220869668664</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022160088768959</v>
+        <v>4.181233072412556</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.007314202286233</v>
+        <v>5.504659377711866</v>
       </c>
       <c r="C2" t="n">
-        <v>6.417684742661399</v>
+        <v>4.37368602241954</v>
       </c>
       <c r="D2" t="n">
-        <v>28.60125586782232</v>
+        <v>23.62870374581223</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.25283324380595</v>
+        <v>20.9603134856694</v>
       </c>
       <c r="C3" t="n">
-        <v>15.15818455357075</v>
+        <v>27.85218236948201</v>
       </c>
       <c r="D3" t="n">
-        <v>41.68500752231957</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.99766095615978</v>
+        <v>35.48036203147973</v>
       </c>
       <c r="C4" t="n">
-        <v>37.71383805864122</v>
+        <v>68.53580723346982</v>
       </c>
       <c r="D4" t="n">
-        <v>31.61325782445154</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.0402359603409</v>
+        <v>30.2869166760141</v>
       </c>
       <c r="C5" t="n">
-        <v>54.95332774521523</v>
+        <v>97.09484795000957</v>
       </c>
       <c r="D5" t="n">
-        <v>31.19503330244241</v>
+        <v>30.43417883165113</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.22392059202629</v>
+        <v>12.67927160034756</v>
       </c>
       <c r="C6" t="n">
-        <v>36.18623863083319</v>
+        <v>55.38627848278806</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>37.63529824230149</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.563785224144926</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>50.82115165804038</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>47.73257338047992</v>
       </c>
     </row>
     <row r="13">
@@ -5605,7 +5605,7 @@
         <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5644,10 +5644,10 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07131003648843</v>
+        <v>18.03810774759376</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8937845237579</v>
+        <v>117.6771791152545</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884308585328927</v>
+        <v>6.012702582531253</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.258641614573417</v>
+        <v>5.948409340031424</v>
       </c>
       <c r="C2" t="n">
-        <v>6.034803138005143</v>
+        <v>8.216246536841556</v>
       </c>
       <c r="D2" t="n">
-        <v>26.39723227178824</v>
+        <v>23.17808154956294</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.76334205001429</v>
+        <v>17.51928778228433</v>
       </c>
       <c r="C3" t="n">
-        <v>19.62513660789374</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D3" t="n">
-        <v>50.94288837336699</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.31374265919825</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="C4" t="n">
-        <v>31.702596865538</v>
+        <v>57.16422357517902</v>
       </c>
       <c r="D4" t="n">
-        <v>38.7220929509027</v>
+        <v>33.96159833300992</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.75138115111408</v>
+        <v>25.59907138823559</v>
       </c>
       <c r="C5" t="n">
-        <v>46.8784528777852</v>
+        <v>83.59581701661591</v>
       </c>
       <c r="D5" t="n">
-        <v>28.8879261974624</v>
+        <v>27.09623663721197</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.06920536538279</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="C6" t="n">
-        <v>42.46549694719579</v>
+        <v>70.76241102670161</v>
       </c>
       <c r="D6" t="n">
-        <v>30.3497485290859</v>
+        <v>29.82647700272235</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.210135066437822</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>23.89475737366311</v>
+        <v>32.21899615797182</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>32.11100391050467</v>
       </c>
     </row>
     <row r="13">
@@ -5916,7 +5916,7 @@
         <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>30.17892442854696</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.065324084753117</v>
+        <v>7.044187412292165</v>
       </c>
       <c r="C21" t="n">
-        <v>66.23741329456047</v>
+        <v>66.03925699023904</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298993063564838</v>
+        <v>4.402617132682603</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.748132808365075</v>
+        <v>6.553165925847459</v>
       </c>
       <c r="C2" t="n">
-        <v>9.201921231905354</v>
+        <v>12.10593094106742</v>
       </c>
       <c r="D2" t="n">
-        <v>22.76378401837079</v>
+        <v>27.15415975176253</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.08655802888974</v>
+        <v>19.53677931451153</v>
       </c>
       <c r="C3" t="n">
-        <v>22.22676802414779</v>
+        <v>27.89145227765188</v>
       </c>
       <c r="D3" t="n">
-        <v>61.37395773098935</v>
+        <v>52.93583621298801</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.76717122984004</v>
+        <v>31.90680038802134</v>
       </c>
       <c r="C4" t="n">
-        <v>42.90826516181109</v>
+        <v>53.84591633482481</v>
       </c>
       <c r="D4" t="n">
-        <v>57.33013893719674</v>
+        <v>49.21304891848411</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.80171232593793</v>
+        <v>34.85204350076177</v>
       </c>
       <c r="C5" t="n">
-        <v>53.82431788533139</v>
+        <v>97.02121687219106</v>
       </c>
       <c r="D5" t="n">
-        <v>37.18369429834795</v>
+        <v>33.33033455917922</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.40129813132547</v>
+        <v>25.64030479181395</v>
       </c>
       <c r="C6" t="n">
-        <v>62.06805335789186</v>
+        <v>106.1436165400524</v>
       </c>
       <c r="D6" t="n">
-        <v>32.88560284915541</v>
+        <v>32.20132469929539</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.00106386316226</v>
+        <v>12.21686843164731</v>
       </c>
       <c r="C7" t="n">
-        <v>46.59178254814513</v>
+        <v>73.00177754008857</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>33.23706852727577</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>26.70353755551324</v>
+        <v>32.62838495064274</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>30.69925071179776</v>
       </c>
     </row>
     <row r="14">
@@ -6238,10 +6238,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.291857153341814</v>
+        <v>7.261294512600226</v>
       </c>
       <c r="C21" t="n">
-        <v>76.56450011008906</v>
+        <v>75.33593056822735</v>
       </c>
       <c r="D21" t="n">
-        <v>6.380375009174087</v>
+        <v>5.445970884450169</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.132576997802325</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C2" t="n">
-        <v>9.412015240614171</v>
+        <v>9.437540680924588</v>
       </c>
       <c r="D2" t="n">
-        <v>18.95263943048467</v>
+        <v>29.240373623287</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.0521968592411</v>
+        <v>21.23520284285851</v>
       </c>
       <c r="C3" t="n">
-        <v>30.61580215693678</v>
+        <v>39.11282853719293</v>
       </c>
       <c r="D3" t="n">
-        <v>65.34512719466771</v>
+        <v>61.79610924381548</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.74012426247764</v>
+        <v>35.4420738710141</v>
       </c>
       <c r="C4" t="n">
-        <v>50.57865997509143</v>
+        <v>62.42246427912495</v>
       </c>
       <c r="D4" t="n">
-        <v>74.66191290796993</v>
+        <v>63.36690557061038</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.20194659410114</v>
+        <v>41.74882112309562</v>
       </c>
       <c r="C5" t="n">
-        <v>68.15783436733483</v>
+        <v>98.49383842856128</v>
       </c>
       <c r="D5" t="n">
-        <v>50.06913291658734</v>
+        <v>43.4914232981337</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.94094057349173</v>
+        <v>37.23278168356029</v>
       </c>
       <c r="C6" t="n">
-        <v>75.67311304334416</v>
+        <v>132.3876961699782</v>
       </c>
       <c r="D6" t="n">
-        <v>37.19253002768617</v>
+        <v>35.30070220160257</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>21.67895280517807</v>
       </c>
       <c r="C7" t="n">
-        <v>71.2051792413169</v>
+        <v>116.2399099305266</v>
       </c>
       <c r="D7" t="n">
-        <v>35.99185258539232</v>
+        <v>35.45287309576081</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.595201150680824</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>46.48084505756524</v>
+        <v>66.09125544989527</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>33.37942194439155</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>32.8374972116473</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.67484588791184</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.506828890375119</v>
+        <v>7.46406002002774</v>
       </c>
       <c r="C21" t="n">
-        <v>86.32853223931386</v>
+        <v>83.97067522531208</v>
       </c>
       <c r="D21" t="n">
-        <v>7.506828890375119</v>
+        <v>6.531052517524272</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_47_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497638245558</v>
+        <v>10.84497621182581</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907211697146</v>
+        <v>37.78907152241592</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.040693624230625</v>
+        <v>6.966481709335367</v>
       </c>
       <c r="C2" t="n">
-        <v>5.837471849451535</v>
+        <v>9.865582679976198</v>
       </c>
       <c r="D2" t="n">
-        <v>23.25171262738146</v>
+        <v>40.56188814866122</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.14898897133403</v>
+        <v>22.79618169261094</v>
       </c>
       <c r="C3" t="n">
-        <v>37.65002445786518</v>
+        <v>38.98029259711961</v>
       </c>
       <c r="D3" t="n">
-        <v>69.69426952448107</v>
+        <v>97.6348091873453</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.21158414469435</v>
+        <v>41.84895938892878</v>
       </c>
       <c r="C4" t="n">
-        <v>80.12435713439919</v>
+        <v>63.07336300704058</v>
       </c>
       <c r="D4" t="n">
-        <v>78.24823727158353</v>
+        <v>108.2789177967892</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.14843349645307</v>
+        <v>52.37624002156735</v>
       </c>
       <c r="C5" t="n">
-        <v>106.9859560702962</v>
+        <v>99.47558613280809</v>
       </c>
       <c r="D5" t="n">
-        <v>54.53608497091033</v>
+        <v>68.74688298988291</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.57116584635595</v>
+        <v>50.31456984264904</v>
       </c>
       <c r="C6" t="n">
-        <v>143.4166498794868</v>
+        <v>141.2833121181585</v>
       </c>
       <c r="D6" t="n">
-        <v>40.69442408873454</v>
+        <v>45.12210623488766</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.87774886752143</v>
+        <v>36.65060529494193</v>
       </c>
       <c r="C7" t="n">
-        <v>154.1481340346087</v>
+        <v>140.0747806942306</v>
       </c>
       <c r="D7" t="n">
-        <v>37.36924461445059</v>
+        <v>38.68675003354981</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.27246819789088</v>
+        <v>19.19316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>108.5665698741335</v>
+        <v>93.71272710887928</v>
       </c>
       <c r="D8" t="n">
-        <v>35.549084370777</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.765624340592267</v>
+        <v>8.542186774651494</v>
       </c>
       <c r="C9" t="n">
-        <v>57.02187015806322</v>
+        <v>47.14843349645305</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>34.59188035913637</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>22.73924032576462</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -962,10 +962,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -979,7 +979,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -993,7 +993,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.65105218841891</v>
+        <v>7.640256993146917</v>
       </c>
       <c r="C21" t="n">
-        <v>92.76900778457927</v>
+        <v>92.63811604190636</v>
       </c>
       <c r="D21" t="n">
-        <v>7.65105218841891</v>
+        <v>7.640256993146917</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.750898125028567</v>
+        <v>9.571058368702154</v>
       </c>
       <c r="C2" t="n">
-        <v>15.63335044242621</v>
+        <v>11.32642326389545</v>
       </c>
       <c r="D2" t="n">
-        <v>20.11110172149591</v>
+        <v>41.56425255469721</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.45333075965055</v>
+        <v>22.71273313774996</v>
       </c>
       <c r="C3" t="n">
-        <v>30.00220984178253</v>
+        <v>38.37651775900782</v>
       </c>
       <c r="D3" t="n">
-        <v>71.07853378746907</v>
+        <v>104.6886664423586</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.82044764777662</v>
+        <v>41.79790850830795</v>
       </c>
       <c r="C4" t="n">
-        <v>86.63334441355555</v>
+        <v>79.02676320105125</v>
       </c>
       <c r="D4" t="n">
-        <v>90.9216183857056</v>
+        <v>127.3464217086708</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>51.86082247683777</v>
+        <v>56.52412407201012</v>
       </c>
       <c r="C5" t="n">
-        <v>124.5101525911018</v>
+        <v>105.8569462104124</v>
       </c>
       <c r="D5" t="n">
-        <v>67.59332943739291</v>
+        <v>86.07472996983911</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.93721887131977</v>
+        <v>59.57245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>154.4858552448696</v>
+        <v>147.8040803697658</v>
       </c>
       <c r="D6" t="n">
-        <v>46.77242412572655</v>
+        <v>54.25923211831272</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.75903951076558</v>
+        <v>46.53189593818607</v>
       </c>
       <c r="C7" t="n">
-        <v>179.5999432672072</v>
+        <v>169.5389927940859</v>
       </c>
       <c r="D7" t="n">
-        <v>40.36357511240336</v>
+        <v>41.80085375142069</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24.70077223884975</v>
+        <v>27.87181732356695</v>
       </c>
       <c r="C8" t="n">
-        <v>151.1253328532327</v>
+        <v>133.5176877775662</v>
       </c>
       <c r="D8" t="n">
-        <v>37.05115835827462</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.6484365108884</v>
+        <v>13.09062388842696</v>
       </c>
       <c r="C9" t="n">
-        <v>92.07811718130831</v>
+        <v>77.43436842476289</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>48.11545498513618</v>
+        <v>41.42484438069417</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.87658719336794</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>33.22921454564179</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
         <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1265,7 +1265,7 @@
         <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1273,7 +1273,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
         <v>22.21695054710532</v>
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>19.83915760741954</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -1318,7 +1318,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.822204086935276</v>
+        <v>7.807117286315775</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7108776192917</v>
+        <v>100.5166350613156</v>
       </c>
       <c r="D21" t="n">
-        <v>8.799979597802185</v>
+        <v>8.783006947105246</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.976700097005335</v>
+        <v>9.746791207762334</v>
       </c>
       <c r="C2" t="n">
-        <v>15.56168286001619</v>
+        <v>10.84438514111027</v>
       </c>
       <c r="D2" t="n">
-        <v>26.05852931382309</v>
+        <v>46.68603032775282</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.76534660315179</v>
+        <v>25.9770442543706</v>
       </c>
       <c r="C3" t="n">
-        <v>43.30489123432681</v>
+        <v>40.39400929123502</v>
       </c>
       <c r="D3" t="n">
-        <v>70.06242491357362</v>
+        <v>109.7053972110598</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.90153179660161</v>
+        <v>41.10872161992669</v>
       </c>
       <c r="C4" t="n">
-        <v>80.43066241812419</v>
+        <v>84.98695351353363</v>
       </c>
       <c r="D4" t="n">
-        <v>101.6678287563912</v>
+        <v>141.7172446034356</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.71985171805373</v>
+        <v>58.26672624704821</v>
       </c>
       <c r="C5" t="n">
-        <v>137.6901155206152</v>
+        <v>120.7795113149639</v>
       </c>
       <c r="D5" t="n">
-        <v>79.30067081053612</v>
+        <v>103.9670818797373</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.09572222006002</v>
+        <v>65.69070238656259</v>
       </c>
       <c r="C6" t="n">
-        <v>172.7198553558456</v>
+        <v>156.4581863827015</v>
       </c>
       <c r="D6" t="n">
-        <v>54.74225198880216</v>
+        <v>65.20768251607315</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>51.68214439466484</v>
+        <v>55.81432048183967</v>
       </c>
       <c r="C7" t="n">
-        <v>196.9670601553333</v>
+        <v>186.5467900224577</v>
       </c>
       <c r="D7" t="n">
-        <v>43.23813239043802</v>
+        <v>45.87314322863646</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>32.96217917008666</v>
+        <v>36.55046702910875</v>
       </c>
       <c r="C8" t="n">
-        <v>186.4240715594268</v>
+        <v>169.4005663677871</v>
       </c>
       <c r="D8" t="n">
-        <v>38.7201294554942</v>
+        <v>39.47116644924301</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.64062358698343</v>
+        <v>18.97031088916111</v>
       </c>
       <c r="C9" t="n">
-        <v>130.57342641253</v>
+        <v>111.9359279951085</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>72.74259614616741</v>
+        <v>61.21196935978863</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>41.75863860013807</v>
+        <v>37.84931924182727</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1545,7 +1545,7 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
         <v>35.1485313074443</v>
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>29.39843500367074</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
         <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.07910495788326</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -1612,7 +1612,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="C17" t="n">
         <v>19.36104647545135</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.976936949783986</v>
+        <v>7.957030037266628</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6886488220838</v>
+        <v>107.4199055030995</v>
       </c>
       <c r="D21" t="n">
-        <v>9.971171187229983</v>
+        <v>9.946287546583283</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.390596717569988</v>
+        <v>9.04582334693011</v>
       </c>
       <c r="C2" t="n">
-        <v>10.83064067325081</v>
+        <v>7.720463946196917</v>
       </c>
       <c r="D2" t="n">
-        <v>21.51892792938584</v>
+        <v>38.61213720802705</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.2996383384403</v>
+        <v>29.40334374219197</v>
       </c>
       <c r="C3" t="n">
-        <v>63.02820261264523</v>
+        <v>57.98201941281663</v>
       </c>
       <c r="D3" t="n">
-        <v>75.90873249236338</v>
+        <v>116.2634718754285</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.32123678793373</v>
+        <v>27.98864530037232</v>
       </c>
       <c r="C4" t="n">
-        <v>111.201580712332</v>
+        <v>104.347999988985</v>
       </c>
       <c r="D4" t="n">
-        <v>94.86529891366503</v>
+        <v>129.0311007691583</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.84575210390879</v>
+        <v>36.98734475749859</v>
       </c>
       <c r="C5" t="n">
-        <v>103.206227408946</v>
+        <v>93.48692513690253</v>
       </c>
       <c r="D5" t="n">
-        <v>54.02066742618075</v>
+        <v>65.89981464756715</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.08056973167303</v>
+        <v>34.65667570761666</v>
       </c>
       <c r="C6" t="n">
-        <v>129.7310868822863</v>
+        <v>122.8480537278119</v>
       </c>
       <c r="D6" t="n">
-        <v>28.45792070300229</v>
+        <v>30.18874190558942</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>24.19419042345839</v>
       </c>
       <c r="C7" t="n">
-        <v>131.0917892003723</v>
+        <v>119.1144672085612</v>
       </c>
       <c r="D7" t="n">
-        <v>27.18852092141116</v>
+        <v>27.72750041104266</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.51590057081509</v>
+        <v>13.18487166803466</v>
       </c>
       <c r="C8" t="n">
-        <v>96.21618375470864</v>
+        <v>82.44717220264712</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>26.20284622634736</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>55.46874528994476</v>
+        <v>46.70468353413349</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>32.74128593663113</v>
+        <v>29.60951076008381</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1842,7 +1842,7 @@
         <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>25.76596849795753</v>
       </c>
       <c r="D11" t="n">
         <v>28.07602084605028</v>
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>1.952696183746906</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>24.71549845441346</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
         <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1895,10 +1895,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0.3583379120500857</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
         <v>22.21695054710532</v>
@@ -1909,7 +1909,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>16.53263133951629</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
         <v>13.37631247036279</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.518002934943821</v>
+        <v>5.461462478725005</v>
       </c>
       <c r="C2" t="n">
-        <v>4.631885668636452</v>
+        <v>3.569634652641403</v>
       </c>
       <c r="D2" t="n">
-        <v>15.60193451589031</v>
+        <v>27.38879745307752</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.96722677732814</v>
+        <v>30.78269926665874</v>
       </c>
       <c r="C3" t="n">
-        <v>53.72614311490671</v>
+        <v>45.18984682648068</v>
       </c>
       <c r="D3" t="n">
-        <v>75.71238295151402</v>
+        <v>119.5817791157827</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.88051418418493</v>
+        <v>39.19431359664541</v>
       </c>
       <c r="C4" t="n">
-        <v>136.9184618250772</v>
+        <v>126.6699975404447</v>
       </c>
       <c r="D4" t="n">
-        <v>108.5596976402038</v>
+        <v>152.5272685748972</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.45367491701582</v>
+        <v>40.96342295969817</v>
       </c>
       <c r="C5" t="n">
-        <v>149.5447190493954</v>
+        <v>137.1746979758856</v>
       </c>
       <c r="D5" t="n">
-        <v>68.20692175254716</v>
+        <v>86.14836104765762</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.55479493055324</v>
+        <v>40.13090090649688</v>
       </c>
       <c r="C6" t="n">
-        <v>149.2933916371082</v>
+        <v>138.8279611098372</v>
       </c>
       <c r="D6" t="n">
-        <v>34.13340418125311</v>
+        <v>37.43403996293088</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.18178755620168</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>158.3401967317426</v>
+        <v>145.1651425407504</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46421209985527</v>
+        <v>30.24273802932299</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>10.59796646734432</v>
       </c>
       <c r="C8" t="n">
-        <v>122.9197213102219</v>
+        <v>106.1465617831651</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>59.46249495082079</v>
+        <v>49.03437083631118</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>33.88011327355743</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.43141351498762</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.14219885286231</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>27.77167905773377</v>
@@ -2178,7 +2178,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
         <v>16.1301147807751</v>
@@ -2192,10 +2192,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
         <v>18.4372218857551</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
         <v>11.33329549782518</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.303981935418017</v>
+        <v>5.589089680277091</v>
       </c>
       <c r="C2" t="n">
-        <v>13.00619358586174</v>
+        <v>10.3711827476633</v>
       </c>
       <c r="D2" t="n">
-        <v>22.67739022039708</v>
+        <v>25.01689499961722</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.68051538995906</v>
+        <v>24.73513340849839</v>
       </c>
       <c r="C3" t="n">
-        <v>35.56381058634071</v>
+        <v>29.55060589782899</v>
       </c>
       <c r="D3" t="n">
-        <v>70.93618037035328</v>
+        <v>115.0510134606837</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.7213321873767</v>
+        <v>47.96230234327367</v>
       </c>
       <c r="C4" t="n">
-        <v>135.3614099661417</v>
+        <v>119.8036540969425</v>
       </c>
       <c r="D4" t="n">
-        <v>119.6632641752352</v>
+        <v>172.2073830542288</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.98229715025711</v>
+        <v>48.08109381548755</v>
       </c>
       <c r="C5" t="n">
-        <v>197.7485313279138</v>
+        <v>181.3042572817797</v>
       </c>
       <c r="D5" t="n">
-        <v>87.71915737445252</v>
+        <v>113.3427724552943</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.23027840880406</v>
+        <v>47.05418571684538</v>
       </c>
       <c r="C6" t="n">
-        <v>190.7928488433252</v>
+        <v>175.2959613317893</v>
       </c>
       <c r="D6" t="n">
-        <v>44.84034464376883</v>
+        <v>50.87809302488671</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.58398531977338</v>
+        <v>31.73990327829938</v>
       </c>
       <c r="C7" t="n">
-        <v>184.5106452838498</v>
+        <v>169.7186526239631</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.68556299720053</v>
+        <v>15.43798264928109</v>
       </c>
       <c r="C8" t="n">
-        <v>162.3074392046039</v>
+        <v>143.8653085803276</v>
       </c>
       <c r="D8" t="n">
-        <v>29.2069942013426</v>
+        <v>28.45595720759379</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>98.29061665378212</v>
+        <v>81.87186804795849</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>28.51093507903161</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>47.83074815090461</v>
+        <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>31.98534020436108</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2601631416254048</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
         <v>25.75615102091507</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
         <v>16.84188186635403</v>
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
         <v>10.38885420633975</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.623229865747478</v>
+        <v>3.439062207976577</v>
       </c>
       <c r="C2" t="n">
-        <v>6.286130550292327</v>
+        <v>5.095270585040946</v>
       </c>
       <c r="D2" t="n">
-        <v>15.81301027230337</v>
+        <v>17.67538566725957</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.15037162966578</v>
+        <v>24.56823629877643</v>
       </c>
       <c r="C3" t="n">
-        <v>44.02156705842698</v>
+        <v>35.7503426501476</v>
       </c>
       <c r="D3" t="n">
-        <v>73.75870502006286</v>
+        <v>113.6176618124834</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.69053815564656</v>
+        <v>52.19952543480291</v>
       </c>
       <c r="C4" t="n">
-        <v>132.3621707296677</v>
+        <v>116.0131262108456</v>
       </c>
       <c r="D4" t="n">
-        <v>128.2398121195353</v>
+        <v>186.1059853032509</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.82307409571988</v>
+        <v>49.57825906446394</v>
       </c>
       <c r="C5" t="n">
-        <v>243.2279937271473</v>
+        <v>219.2242623583128</v>
       </c>
       <c r="D5" t="n">
-        <v>92.35791527701869</v>
+        <v>116.6316272645211</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.13969557810609</v>
+        <v>37.95731148929444</v>
       </c>
       <c r="C6" t="n">
-        <v>222.6721602956276</v>
+        <v>205.7262131726234</v>
       </c>
       <c r="D6" t="n">
-        <v>43.91455655866408</v>
+        <v>49.50953672516665</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.042878103817369</v>
+        <v>10.18072369303942</v>
       </c>
       <c r="C7" t="n">
-        <v>200.3805969229995</v>
+        <v>179.8993763170025</v>
       </c>
       <c r="D7" t="n">
-        <v>32.57831581772616</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>118.580396457451</v>
+        <v>101.2230970463674</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>36.49843440078366</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>30.95155987178918</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.0542014123786</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.20360698987336</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.56743447752142</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>14.53673825678252</v>
       </c>
       <c r="D12" t="n">
         <v>21.04572553593887</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
         <v>14.13520344574558</v>
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
         <v>8.679631453246051</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.722787294503905</v>
+        <v>3.587306111317845</v>
       </c>
       <c r="C2" t="n">
-        <v>5.048146695237099</v>
+        <v>11.38532812615026</v>
       </c>
       <c r="D2" t="n">
-        <v>18.99485458176729</v>
+        <v>14.33940696822891</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.90783888898781</v>
+        <v>18.55012287174348</v>
       </c>
       <c r="C3" t="n">
-        <v>34.46425315758428</v>
+        <v>28.10743677258618</v>
       </c>
       <c r="D3" t="n">
-        <v>69.5960947540564</v>
+        <v>104.0210780034708</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.20631555327462</v>
+        <v>49.92776124717579</v>
       </c>
       <c r="C4" t="n">
-        <v>122.7901306132613</v>
+        <v>103.4035586974995</v>
       </c>
       <c r="D4" t="n">
-        <v>134.0979006707761</v>
+        <v>196.1757715057104</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.07604620824608</v>
+        <v>60.74563920027141</v>
       </c>
       <c r="C5" t="n">
-        <v>242.9334694158733</v>
+        <v>218.389776809703</v>
       </c>
       <c r="D5" t="n">
-        <v>112.6310053697153</v>
+        <v>145.4950097693773</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.16235789076178</v>
+        <v>48.06047711369836</v>
       </c>
       <c r="C6" t="n">
-        <v>296.0911806100211</v>
+        <v>266.5062135425434</v>
       </c>
       <c r="D6" t="n">
-        <v>56.75483478250812</v>
+        <v>66.53598715991909</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.74450891718435</v>
+        <v>20.66088043587412</v>
       </c>
       <c r="C7" t="n">
-        <v>250.9847823384013</v>
+        <v>230.3239019025272</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>37.72856427420492</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>175.9095536469435</v>
+        <v>152.9612010601743</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>74.32811868852599</v>
+        <v>63.34530712111692</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
-        <v>32.45657910239955</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.05772749256809</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>22.7451308119901</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>23.45591614986479</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>16.70640068316797</v>
       </c>
       <c r="D12" t="n">
         <v>21.04572553593887</v>
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.56913593102267</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
         <v>13.82791641431633</v>
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>7.852999886270235</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.581996462169111</v>
+        <v>2.565306751196915</v>
       </c>
       <c r="C2" t="n">
-        <v>2.817615911188346</v>
+        <v>6.923284810348507</v>
       </c>
       <c r="D2" t="n">
-        <v>13.79159174925919</v>
+        <v>11.58854990092935</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.05862712481433</v>
+        <v>16.11047982669016</v>
       </c>
       <c r="C3" t="n">
-        <v>28.66212422548563</v>
+        <v>35.58344554042564</v>
       </c>
       <c r="D3" t="n">
-        <v>68.7616092054466</v>
+        <v>94.90555056953917</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.00738062221102</v>
+        <v>45.52462279362884</v>
       </c>
       <c r="C4" t="n">
-        <v>110.1678003797601</v>
+        <v>92.87431456945251</v>
       </c>
       <c r="D4" t="n">
-        <v>137.1481907878709</v>
+        <v>203.2463184716959</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.101211795658</v>
+        <v>66.8570186592078</v>
       </c>
       <c r="C5" t="n">
-        <v>244.9215085169731</v>
+        <v>213.7510189071369</v>
       </c>
       <c r="D5" t="n">
-        <v>126.6945412330509</v>
+        <v>164.7127210800086</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.04539104523617</v>
+        <v>54.86300695642451</v>
       </c>
       <c r="C6" t="n">
-        <v>337.2283729133709</v>
+        <v>303.4169819791107</v>
       </c>
       <c r="D6" t="n">
-        <v>67.01900703040852</v>
+        <v>80.26180181299375</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.64847756861741</v>
+        <v>18.32530264747096</v>
       </c>
       <c r="C7" t="n">
-        <v>306.4996697704457</v>
+        <v>281.8263864673148</v>
       </c>
       <c r="D7" t="n">
-        <v>40.12402867256714</v>
+        <v>42.69915290080652</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>220.7214276072891</v>
+        <v>191.0137420767806</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>31.79389940203295</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>78.21093085882212</v>
+        <v>67.11718180083317</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>32.31422568528377</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>21.67895280517806</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
         <v>19.52696183746906</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
         <v>15.60978849752428</v>
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.541163969218245</v>
+        <v>5.244496236086461</v>
       </c>
       <c r="C2" t="n">
-        <v>3.73653176236336</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="D2" t="n">
-        <v>15.8051562906694</v>
+        <v>16.50317890838888</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.53553552490002</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C3" t="n">
-        <v>20.96522222419064</v>
+        <v>31.50428382928014</v>
       </c>
       <c r="D3" t="n">
-        <v>64.49100669197297</v>
+        <v>84.84263660100936</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.6087499965578</v>
+        <v>38.53065214857457</v>
       </c>
       <c r="C4" t="n">
-        <v>93.84428130124836</v>
+        <v>90.79399118415351</v>
       </c>
       <c r="D4" t="n">
-        <v>138.5648527250991</v>
+        <v>202.9144877476605</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.07037670619884</v>
+        <v>67.59332943739291</v>
       </c>
       <c r="C5" t="n">
-        <v>225.0902048911875</v>
+        <v>196.1286476159066</v>
       </c>
       <c r="D5" t="n">
-        <v>139.9235915477767</v>
+        <v>187.9065105928395</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.54478183152831</v>
+        <v>65.85170901005907</v>
       </c>
       <c r="C6" t="n">
-        <v>361.3391147819684</v>
+        <v>317.7868231261713</v>
       </c>
       <c r="D6" t="n">
-        <v>81.71086142446205</v>
+        <v>100.3071264383051</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.42239785920016</v>
+        <v>32.63820242768521</v>
       </c>
       <c r="C7" t="n">
-        <v>373.3331264847516</v>
+        <v>339.8565115176395</v>
       </c>
       <c r="D7" t="n">
-        <v>46.71155576806323</v>
+        <v>51.26293812495145</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>8.92899537012474</v>
       </c>
       <c r="C8" t="n">
-        <v>287.3133743863503</v>
+        <v>258.0229316301467</v>
       </c>
       <c r="D8" t="n">
-        <v>35.29873870619407</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>144.2187377538564</v>
+        <v>121.9203021472986</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>51.24723016168351</v>
+        <v>45.83780031128358</v>
       </c>
       <c r="D10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.65909686691488</v>
+        <v>18.00819813899924</v>
       </c>
       <c r="D12" t="n">
         <v>19.96089432274615</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D13" t="n">
         <v>15.86995163914969</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
         <v>6.091744504851459</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.864379948093698</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C2" t="n">
-        <v>14.47979688993621</v>
+        <v>9.591675070491338</v>
       </c>
       <c r="D2" t="n">
-        <v>5.501714134599125</v>
+        <v>13.03171902617216</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.616357631817749</v>
+        <v>3.87201294554942</v>
       </c>
       <c r="C2" t="n">
-        <v>2.21285932537231</v>
+        <v>4.275511251994859</v>
       </c>
       <c r="D2" t="n">
-        <v>11.75839225376405</v>
+        <v>12.27871853701486</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.23181563138926</v>
+        <v>17.53401399784803</v>
       </c>
       <c r="C3" t="n">
-        <v>23.09070600388498</v>
+        <v>35.92214849839079</v>
       </c>
       <c r="D3" t="n">
-        <v>70.42567156414495</v>
+        <v>92.06339096574465</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.56741878198821</v>
+        <v>52.17399999449249</v>
       </c>
       <c r="C4" t="n">
-        <v>131.8006110428385</v>
+        <v>126.1594887342364</v>
       </c>
       <c r="D4" t="n">
-        <v>140.5303116290012</v>
+        <v>203.5909119158866</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.65569395991241</v>
+        <v>37.08551952792327</v>
       </c>
       <c r="C5" t="n">
-        <v>319.6570525027615</v>
+        <v>278.1045809205153</v>
       </c>
       <c r="D5" t="n">
-        <v>124.2892593576462</v>
+        <v>164.050041379642</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.87802660496192</v>
+        <v>20.24658290468198</v>
       </c>
       <c r="C6" t="n">
-        <v>306.0735912668026</v>
+        <v>276.7703857904439</v>
       </c>
       <c r="D6" t="n">
-        <v>66.29447722467438</v>
+        <v>77.8467024605466</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>5.868887775987432</v>
       </c>
       <c r="C7" t="n">
-        <v>202.057422001853</v>
+        <v>181.456428175938</v>
       </c>
       <c r="D7" t="n">
-        <v>30.30262463928205</v>
+        <v>30.18285141936394</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.50207398749762</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>106.3134588928871</v>
+        <v>89.87409358527424</v>
       </c>
       <c r="D8" t="n">
-        <v>24.36697801940583</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.2218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>39.04999668412111</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D9" t="n">
-        <v>19.63593583264045</v>
+        <v>19.41406085148067</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>20.35653864755762</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>18.64829764216817</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.9264920953685</v>
+        <v>14.39340309196248</v>
       </c>
       <c r="D11" t="n">
         <v>15.99267010218054</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="D12" t="n">
         <v>12.80100831567416</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.8226478228966</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>4.916592502868027</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.970809610779853</v>
+        <v>8.08861933528947</v>
       </c>
       <c r="C2" t="n">
-        <v>7.740098900281853</v>
+        <v>10.20035864712436</v>
       </c>
       <c r="D2" t="n">
-        <v>7.001824626688252</v>
+        <v>10.6333093846972</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.57895340806514</v>
+        <v>20.37126486312131</v>
       </c>
       <c r="C3" t="n">
-        <v>36.48665342833271</v>
+        <v>24.17062847855647</v>
       </c>
       <c r="D3" t="n">
-        <v>7.755806863549802</v>
+        <v>14.08317081742049</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4571,7 +4571,7 @@
         <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
         <v>32.8453511932813</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
         <v>21.69662426385451</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
         <v>22.74218556887735</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>50.1084028247572</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>5.375068680751286</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
         <v>42.28387362191012</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39739370469528</v>
+        <v>13.39647365410934</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13929645399294</v>
+        <v>70.13447971857242</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576163965258268</v>
+        <v>1.576055724012863</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.218970795776044</v>
+        <v>5.244496236086461</v>
       </c>
       <c r="C2" t="n">
-        <v>5.832563110930301</v>
+        <v>6.977280934082081</v>
       </c>
       <c r="D2" t="n">
-        <v>18.88980757741288</v>
+        <v>17.54481322259475</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.3445777486574</v>
+        <v>25.00511402716626</v>
       </c>
       <c r="C3" t="n">
-        <v>32.54493639578177</v>
+        <v>33.934109397291</v>
       </c>
       <c r="D3" t="n">
-        <v>11.76133749687679</v>
+        <v>19.61041039233004</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>16.8978414854961</v>
+        <v>23.44511692511808</v>
       </c>
       <c r="C4" t="n">
-        <v>56.13044324260714</v>
+        <v>37.3820073346058</v>
       </c>
       <c r="D4" t="n">
-        <v>19.13131751265759</v>
+        <v>22.44962475301181</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.3139636433765</v>
       </c>
       <c r="D7" t="n">
         <v>34.97378021608837</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
@@ -4927,7 +4927,7 @@
         <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>40.60312155223957</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>49.68134257340984</v>
       </c>
     </row>
     <row r="11">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43804107257887</v>
+        <v>15.43598738588758</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12801861544003</v>
+        <v>86.11656120547811</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250113910016605</v>
+        <v>3.249681554923702</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.359761628110838</v>
+        <v>6.178138302825178</v>
       </c>
       <c r="C2" t="n">
-        <v>7.428884878035614</v>
+        <v>6.46971737098648</v>
       </c>
       <c r="D2" t="n">
-        <v>25.37425116396306</v>
+        <v>29.27768003604838</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.12582793705961</v>
+        <v>21.1468455494763</v>
       </c>
       <c r="C3" t="n">
-        <v>26.64954143177967</v>
+        <v>29.86476516318797</v>
       </c>
       <c r="D3" t="n">
-        <v>24.14117604742907</v>
+        <v>29.09409321535422</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.38352886165779</v>
+        <v>37.16504109196725</v>
       </c>
       <c r="C4" t="n">
-        <v>70.82033414125216</v>
+        <v>64.91119470939061</v>
       </c>
       <c r="D4" t="n">
-        <v>20.73942025221387</v>
+        <v>27.23564481121501</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>14.55440971545897</v>
+        <v>19.61041039233004</v>
       </c>
       <c r="C5" t="n">
-        <v>60.37748381117885</v>
+        <v>41.01251034491051</v>
       </c>
       <c r="D5" t="n">
-        <v>29.550605897829</v>
+        <v>30.99868376159304</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
         <v>37.4890178343687</v>
@@ -5221,7 +5221,7 @@
         <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.70768553050848</v>
       </c>
       <c r="D8" t="n">
         <v>37.88564390688441</v>
@@ -5238,7 +5238,7 @@
         <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.49062147687869</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>49.57727731675966</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.67707142522758</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72493228965022</v>
+        <v>16.72231519675395</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0220869668664</v>
+        <v>102.0061227001991</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181233072412556</v>
+        <v>4.180578799188488</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.504659377711866</v>
+        <v>6.284167054883833</v>
       </c>
       <c r="C2" t="n">
-        <v>4.37368602241954</v>
+        <v>5.154175447295755</v>
       </c>
       <c r="D2" t="n">
-        <v>23.62870374581223</v>
+        <v>32.06388002070083</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.9603134856694</v>
+        <v>21.09284942574272</v>
       </c>
       <c r="C3" t="n">
-        <v>27.85218236948201</v>
+        <v>27.13059780686061</v>
       </c>
       <c r="D3" t="n">
-        <v>38.05254101660637</v>
+        <v>44.87077882260047</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.48036203147973</v>
+        <v>39.27088991757666</v>
       </c>
       <c r="C4" t="n">
-        <v>68.53580723346982</v>
+        <v>70.28429989473339</v>
       </c>
       <c r="D4" t="n">
-        <v>27.77167905773377</v>
+        <v>35.22510762837556</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.2869166760141</v>
+        <v>37.11006322052944</v>
       </c>
       <c r="C5" t="n">
-        <v>97.09484795000957</v>
+        <v>82.39317607891357</v>
       </c>
       <c r="D5" t="n">
-        <v>30.43417883165113</v>
+        <v>33.74757733348411</v>
       </c>
     </row>
     <row r="6">
@@ -5501,10 +5501,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.67927160034756</v>
+        <v>15.97990738202533</v>
       </c>
       <c r="C6" t="n">
-        <v>55.38627848278806</v>
+        <v>39.56737772425921</v>
       </c>
       <c r="D6" t="n">
         <v>37.63529824230149</v>
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.76470901281281</v>
       </c>
     </row>
     <row r="8">
@@ -5529,10 +5529,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
         <v>39.30426933952106</v>
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.3781214015178</v>
       </c>
     </row>
     <row r="10">
@@ -5563,7 +5563,7 @@
         <v>33.31069960509428</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>48.54251523648354</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.6434553235717</v>
       </c>
     </row>
     <row r="12">
@@ -5591,7 +5591,7 @@
         <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>47.73257338047992</v>
+        <v>47.51560713784138</v>
       </c>
     </row>
     <row r="13">
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
         <v>45.26838664282043</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>39.00483628972577</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03810774759376</v>
+        <v>18.03461847886948</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6771791152545</v>
+        <v>117.65441579072</v>
       </c>
       <c r="D21" t="n">
-        <v>6.012702582531253</v>
+        <v>6.011539492956493</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.948409340031424</v>
+        <v>7.63308840051895</v>
       </c>
       <c r="C2" t="n">
-        <v>8.216246536841556</v>
+        <v>5.789366211943441</v>
       </c>
       <c r="D2" t="n">
-        <v>23.17808154956294</v>
+        <v>44.2463872826995</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.51928778228433</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="C3" t="n">
-        <v>20.61179305066178</v>
+        <v>21.71135047941821</v>
       </c>
       <c r="D3" t="n">
-        <v>44.12955930589413</v>
+        <v>54.87478792887547</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.55471281509523</v>
+        <v>29.08623923372025</v>
       </c>
       <c r="C4" t="n">
-        <v>57.16422357517902</v>
+        <v>56.99830821316132</v>
       </c>
       <c r="D4" t="n">
-        <v>33.96159833300992</v>
+        <v>41.73409490753191</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.59907138823559</v>
+        <v>29.08427573831176</v>
       </c>
       <c r="C5" t="n">
-        <v>83.59581701661591</v>
+        <v>79.66882619962867</v>
       </c>
       <c r="D5" t="n">
-        <v>27.09623663721197</v>
+        <v>31.24412068765475</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.36984114706057</v>
+        <v>17.75098024048658</v>
       </c>
       <c r="C6" t="n">
-        <v>70.76241102670161</v>
+        <v>57.47936458824226</v>
       </c>
       <c r="D6" t="n">
-        <v>29.82647700272235</v>
+        <v>30.51075515258238</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>32.21899615797182</v>
+        <v>25.03260296288517</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -5840,7 +5840,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
         <v>18.44213062427633</v>
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
         <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.28593492830985</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.02599277086271</v>
       </c>
     </row>
     <row r="11">
@@ -5899,7 +5899,7 @@
         <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
         <v>32.11100391050467</v>
@@ -5913,7 +5913,7 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="D13" t="n">
         <v>30.17892442854696</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5983,7 +5983,7 @@
         <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.044187412292165</v>
+        <v>7.042108848184713</v>
       </c>
       <c r="C21" t="n">
-        <v>66.03925699023904</v>
+        <v>66.01977045173169</v>
       </c>
       <c r="D21" t="n">
-        <v>4.402617132682603</v>
+        <v>4.401318030115446</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.553165925847459</v>
+        <v>6.724971774090651</v>
       </c>
       <c r="C2" t="n">
-        <v>12.10593094106742</v>
+        <v>8.301658587111028</v>
       </c>
       <c r="D2" t="n">
-        <v>27.15415975176253</v>
+        <v>39.02447124381072</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.53677931451153</v>
+        <v>23.4539526544563</v>
       </c>
       <c r="C3" t="n">
-        <v>27.89145227765188</v>
+        <v>22.25131171675396</v>
       </c>
       <c r="D3" t="n">
-        <v>52.93583621298801</v>
+        <v>78.78034452728531</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.90680038802134</v>
+        <v>33.71910665006095</v>
       </c>
       <c r="C4" t="n">
-        <v>53.84591633482481</v>
+        <v>54.94351026817274</v>
       </c>
       <c r="D4" t="n">
-        <v>49.21304891848411</v>
+        <v>60.81436153956867</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.85204350076177</v>
+        <v>37.79728661350221</v>
       </c>
       <c r="C5" t="n">
-        <v>97.02121687219106</v>
+        <v>95.25407100454679</v>
       </c>
       <c r="D5" t="n">
-        <v>33.33033455917922</v>
+        <v>39.39262663290327</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.64030479181395</v>
+        <v>29.98748362621883</v>
       </c>
       <c r="C6" t="n">
-        <v>106.1436165400524</v>
+        <v>97.52976218299091</v>
       </c>
       <c r="D6" t="n">
-        <v>32.20132469929539</v>
+        <v>34.05290086950487</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.21686843164731</v>
+        <v>14.67221943996858</v>
       </c>
       <c r="C7" t="n">
-        <v>73.00177754008857</v>
+        <v>58.20978488020188</v>
       </c>
       <c r="D7" t="n">
-        <v>33.23706852727577</v>
+        <v>33.41672835715293</v>
       </c>
     </row>
     <row r="8">
@@ -6151,10 +6151,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>32.62838495064274</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D8" t="n">
         <v>31.2097595180061</v>
@@ -6171,7 +6171,7 @@
         <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.20008090968388</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6199,7 +6199,7 @@
         <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6207,10 +6207,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6227,7 +6227,7 @@
         <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.261294512600226</v>
+        <v>7.256468312021784</v>
       </c>
       <c r="C21" t="n">
-        <v>75.33593056822735</v>
+        <v>75.28585873722602</v>
       </c>
       <c r="D21" t="n">
-        <v>5.445970884450169</v>
+        <v>5.442351234016338</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.124723016168351</v>
+        <v>6.695519342963247</v>
       </c>
       <c r="C2" t="n">
-        <v>9.437540680924588</v>
+        <v>12.51433798603409</v>
       </c>
       <c r="D2" t="n">
-        <v>29.240373623287</v>
+        <v>36.20587358491812</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.23520284285851</v>
+        <v>23.23305942100077</v>
       </c>
       <c r="C3" t="n">
-        <v>39.11282853719293</v>
+        <v>28.11234551110741</v>
       </c>
       <c r="D3" t="n">
-        <v>61.79610924381548</v>
+        <v>90.91474615177589</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.4420738710141</v>
+        <v>39.9217886454923</v>
       </c>
       <c r="C4" t="n">
-        <v>62.42246427912495</v>
+        <v>55.39020547360504</v>
       </c>
       <c r="D4" t="n">
-        <v>63.36690557061038</v>
+        <v>84.64236006934301</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.74882112309562</v>
+        <v>44.96404485450392</v>
       </c>
       <c r="C5" t="n">
-        <v>98.49383842856128</v>
+        <v>98.76381904722915</v>
       </c>
       <c r="D5" t="n">
-        <v>43.4914232981337</v>
+        <v>52.327152636355</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.23278168356029</v>
+        <v>40.97618567985338</v>
       </c>
       <c r="C6" t="n">
-        <v>132.3876961699782</v>
+        <v>125.3436563920073</v>
       </c>
       <c r="D6" t="n">
-        <v>35.30070220160257</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.67895280517807</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C7" t="n">
-        <v>116.2399099305266</v>
+        <v>102.4659896399438</v>
       </c>
       <c r="D7" t="n">
-        <v>35.45287309576081</v>
+        <v>35.57264631567892</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>11.26555490623215</v>
       </c>
       <c r="C8" t="n">
-        <v>66.09125544989527</v>
+        <v>53.49052366588747</v>
       </c>
       <c r="D8" t="n">
         <v>33.37942194439155</v>
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>32.8374972116473</v>
+        <v>29.17656002251095</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.33538216642069</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.30717352490479</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.00617789032851</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.06370009425158</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6546,7 +6546,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
         <v>21.20280516861837</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6577,7 +6577,7 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
         <v>26.45221014322606</v>
@@ -6605,7 +6605,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.46406002002774</v>
+        <v>7.456356709960037</v>
       </c>
       <c r="C21" t="n">
-        <v>83.97067522531208</v>
+        <v>83.88401298705041</v>
       </c>
       <c r="D21" t="n">
-        <v>6.531052517524272</v>
+        <v>6.524312121215032</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_47_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_47_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497621182581</v>
+        <v>10.84497610535536</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907152241592</v>
+        <v>37.78907115142205</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.966481709335367</v>
+        <v>1.48342078111693</v>
       </c>
       <c r="C2" t="n">
-        <v>9.865582679976198</v>
+        <v>3.381139093426015</v>
       </c>
       <c r="D2" t="n">
-        <v>40.56188814866122</v>
+        <v>12.97281416391735</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.79618169261094</v>
+        <v>11.05447914981909</v>
       </c>
       <c r="C3" t="n">
-        <v>38.98029259711961</v>
+        <v>41.18922493167493</v>
       </c>
       <c r="D3" t="n">
-        <v>97.6348091873453</v>
+        <v>56.8971881996239</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.84895938892878</v>
+        <v>19.23341927389927</v>
       </c>
       <c r="C4" t="n">
-        <v>63.07336300704058</v>
+        <v>119.7143150558561</v>
       </c>
       <c r="D4" t="n">
-        <v>108.2789177967892</v>
+        <v>63.73702445511142</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.37624002156735</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="C5" t="n">
-        <v>99.47558613280809</v>
+        <v>120.7304239297515</v>
       </c>
       <c r="D5" t="n">
-        <v>68.74688298988291</v>
+        <v>44.05592822807562</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.31456984264904</v>
+        <v>13.00128484734051</v>
       </c>
       <c r="C6" t="n">
-        <v>141.2833121181585</v>
+        <v>74.3045567436241</v>
       </c>
       <c r="D6" t="n">
-        <v>45.12210623488766</v>
+        <v>29.26295382048468</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.65060529494193</v>
+        <v>6.28809404570082</v>
       </c>
       <c r="C7" t="n">
-        <v>140.0747806942306</v>
+        <v>38.26754376383641</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>29.58398531977338</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.19316761802514</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>93.71272710887928</v>
+        <v>28.45595720759379</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.542186774651494</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>47.14843349645305</v>
+        <v>31.8390597964283</v>
       </c>
       <c r="D9" t="n">
-        <v>33.72499713628642</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>34.59188035913637</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>31.09685853201771</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>22.73924032576462</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.640256993146917</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.63811604190636</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.640256993146917</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.571058368702154</v>
+        <v>1.527599427808037</v>
       </c>
       <c r="C2" t="n">
-        <v>11.32642326389545</v>
+        <v>3.458697162061513</v>
       </c>
       <c r="D2" t="n">
-        <v>41.56425255469721</v>
+        <v>14.08611606053323</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.71273313774996</v>
+        <v>7.932521450314228</v>
       </c>
       <c r="C3" t="n">
-        <v>38.37651775900782</v>
+        <v>24.84312565596554</v>
       </c>
       <c r="D3" t="n">
-        <v>104.6886664423586</v>
+        <v>54.09920724252049</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.79790850830795</v>
+        <v>20.59903033050658</v>
       </c>
       <c r="C4" t="n">
-        <v>79.02676320105125</v>
+        <v>110.3081903014674</v>
       </c>
       <c r="D4" t="n">
-        <v>127.3464217086708</v>
+        <v>77.15064333823558</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.52412407201012</v>
+        <v>24.47006152835176</v>
       </c>
       <c r="C5" t="n">
-        <v>105.8569462104124</v>
+        <v>177.1809169239431</v>
       </c>
       <c r="D5" t="n">
-        <v>86.07472996983911</v>
+        <v>56.27868714594842</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.57245069369646</v>
+        <v>19.48180144307371</v>
       </c>
       <c r="C6" t="n">
-        <v>147.8040803697658</v>
+        <v>135.9700935427747</v>
       </c>
       <c r="D6" t="n">
-        <v>54.25923211831272</v>
+        <v>35.86422538384024</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>46.53189593818607</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C7" t="n">
-        <v>169.5389927940859</v>
+        <v>73.30121058988385</v>
       </c>
       <c r="D7" t="n">
-        <v>41.80085375142069</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.87181732356695</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>133.5176877775662</v>
+        <v>39.8884092235479</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>32.62838495064274</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.09062388842696</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>77.43436842476289</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>41.42484438069417</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>39.14718970684157</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>31.8076438698924</v>
+        <v>34.29539255245382</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.56010457970196</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>38.18605870438393</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.8266315669758143</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>46.33947338815369</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.807117286315775</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.5166350613156</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.783006947105246</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.746791207762334</v>
+        <v>0.8089601082993717</v>
       </c>
       <c r="C2" t="n">
-        <v>10.84438514111027</v>
+        <v>1.460840583919254</v>
       </c>
       <c r="D2" t="n">
-        <v>46.68603032775282</v>
+        <v>9.475828841390213</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.9770442543706</v>
+        <v>7.549639845657971</v>
       </c>
       <c r="C3" t="n">
-        <v>40.39400929123502</v>
+        <v>20.70996782108647</v>
       </c>
       <c r="D3" t="n">
-        <v>109.7053972110598</v>
+        <v>55.23312584092555</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.10872161992669</v>
+        <v>22.64106555533994</v>
       </c>
       <c r="C4" t="n">
-        <v>84.98695351353363</v>
+        <v>101.6678287563912</v>
       </c>
       <c r="D4" t="n">
-        <v>141.7172446034356</v>
+        <v>85.20391975617218</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.26672624704821</v>
+        <v>24.91184799526282</v>
       </c>
       <c r="C5" t="n">
-        <v>120.7795113149639</v>
+        <v>208.4004939189917</v>
       </c>
       <c r="D5" t="n">
-        <v>103.9670818797373</v>
+        <v>63.07728999785758</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.69070238656259</v>
+        <v>15.13462260866883</v>
       </c>
       <c r="C6" t="n">
-        <v>156.4581863827015</v>
+        <v>176.9462792226282</v>
       </c>
       <c r="D6" t="n">
-        <v>65.20768251607315</v>
+        <v>36.70951015719674</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>55.81432048183967</v>
+        <v>4.431609136970102</v>
       </c>
       <c r="C7" t="n">
-        <v>186.5467900224577</v>
+        <v>70.36676670189013</v>
       </c>
       <c r="D7" t="n">
-        <v>45.87314322863646</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>36.55046702910875</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>169.4005663677871</v>
+        <v>39.80496066868692</v>
       </c>
       <c r="D8" t="n">
-        <v>39.47116644924301</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18.97031088916111</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>111.9359279951085</v>
+        <v>26.62499773917349</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>40.93593402397924</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>61.21196935978863</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.84931924182727</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.39843500367074</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.07910495788326</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.4722206457427158</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>40.12893741108837</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.957030037266628</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.4199055030995</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.946287546583283</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.04582334693011</v>
+        <v>1.075995483854504</v>
       </c>
       <c r="C2" t="n">
-        <v>7.720463946196917</v>
+        <v>3.697261854193488</v>
       </c>
       <c r="D2" t="n">
-        <v>38.61213720802705</v>
+        <v>12.13931036301181</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>29.40334374219197</v>
+        <v>5.090361846519713</v>
       </c>
       <c r="C3" t="n">
-        <v>57.98201941281663</v>
+        <v>12.21785017935156</v>
       </c>
       <c r="D3" t="n">
-        <v>116.2634718754285</v>
+        <v>50.67781649322035</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.98864530037232</v>
+        <v>18.92711399017426</v>
       </c>
       <c r="C4" t="n">
-        <v>104.347999988985</v>
+        <v>75.27452347541994</v>
       </c>
       <c r="D4" t="n">
-        <v>129.0311007691583</v>
+        <v>92.69563648727959</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.98734475749859</v>
+        <v>29.550605897829</v>
       </c>
       <c r="C5" t="n">
-        <v>93.48692513690253</v>
+        <v>199.6138519659828</v>
       </c>
       <c r="D5" t="n">
-        <v>65.89981464756715</v>
+        <v>77.5826123281042</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.65667570761666</v>
+        <v>23.2252054393668</v>
       </c>
       <c r="C6" t="n">
-        <v>122.8480537278119</v>
+        <v>256.1212863270207</v>
       </c>
       <c r="D6" t="n">
-        <v>30.18874190558942</v>
+        <v>46.81267578160067</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.19419042345839</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>119.1144672085612</v>
+        <v>156.7831448728071</v>
       </c>
       <c r="D7" t="n">
-        <v>27.72750041104266</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.18487166803466</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>82.44717220264712</v>
+        <v>63.92159302350981</v>
       </c>
       <c r="D8" t="n">
-        <v>26.20284622634736</v>
+        <v>37.46840113257952</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>46.70468353413349</v>
+        <v>36.83124687252333</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.60951076008381</v>
+        <v>30.17892442854695</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.8871654339364</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>25.76596849795753</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.952696183746906</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>23.86628669023996</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>30.8092064546734</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>24.27567548291088</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3583379120500857</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>23.65030219530566</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.5585576904542</v>
-      </c>
-      <c r="D15" t="n">
-        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.19842051391164</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>47.6942852200143</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.461462478725005</v>
+        <v>0.5546874528994479</v>
       </c>
       <c r="C2" t="n">
-        <v>3.569634652641403</v>
+        <v>2.036144738607885</v>
       </c>
       <c r="D2" t="n">
-        <v>27.38879745307752</v>
+        <v>9.395325529641976</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>30.78269926665874</v>
+        <v>4.540583132141498</v>
       </c>
       <c r="C3" t="n">
-        <v>45.18984682648068</v>
+        <v>13.64138435050943</v>
       </c>
       <c r="D3" t="n">
-        <v>119.5817791157827</v>
+        <v>49.11683764346792</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.19431359664541</v>
+        <v>15.71090851106171</v>
       </c>
       <c r="C4" t="n">
-        <v>126.6699975404447</v>
+        <v>55.82413795888213</v>
       </c>
       <c r="D4" t="n">
-        <v>152.5272685748972</v>
+        <v>97.64757190750051</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.96342295969817</v>
+        <v>31.02322745419922</v>
       </c>
       <c r="C5" t="n">
-        <v>137.1746979758856</v>
+        <v>180.4697717331699</v>
       </c>
       <c r="D5" t="n">
-        <v>86.14836104765762</v>
+        <v>88.52909923045614</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.13090090649688</v>
+        <v>28.21641076775758</v>
       </c>
       <c r="C6" t="n">
-        <v>138.8279611098372</v>
+        <v>291.9452600549868</v>
       </c>
       <c r="D6" t="n">
-        <v>37.43403996293088</v>
+        <v>56.07055663264809</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>10.65981657271187</v>
       </c>
       <c r="C7" t="n">
-        <v>145.1651425407504</v>
+        <v>233.378119010439</v>
       </c>
       <c r="D7" t="n">
-        <v>30.24273802932299</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.59796646734432</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>106.1465617831651</v>
+        <v>102.2244797046991</v>
       </c>
       <c r="D8" t="n">
-        <v>26.95388322009618</v>
+        <v>40.22220344299182</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>49.03437083631118</v>
+        <v>47.37030847761284</v>
       </c>
       <c r="D9" t="n">
-        <v>28.06718511671205</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>29.46715734296802</v>
+        <v>32.88363935374691</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>28.43141351498762</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>29.14219885286231</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>14.74977750860408</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.53373626040754</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>40.5049467818149</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.589089680277091</v>
+        <v>1.393099992326224</v>
       </c>
       <c r="C2" t="n">
-        <v>10.3711827476633</v>
+        <v>7.717518703084177</v>
       </c>
       <c r="D2" t="n">
-        <v>25.01689499961722</v>
+        <v>13.02779203535517</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.73513340849839</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C3" t="n">
-        <v>29.55060589782899</v>
+        <v>10.61760142142925</v>
       </c>
       <c r="D3" t="n">
-        <v>115.0510134606837</v>
+        <v>45.5236410459246</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>47.96230234327367</v>
+        <v>12.4181267110179</v>
       </c>
       <c r="C4" t="n">
-        <v>119.8036540969425</v>
+        <v>44.88648678586841</v>
       </c>
       <c r="D4" t="n">
-        <v>172.2073830542288</v>
+        <v>99.57474265093698</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.08109381548755</v>
+        <v>28.397052345339</v>
       </c>
       <c r="C5" t="n">
-        <v>181.3042572817797</v>
+        <v>144.734155298586</v>
       </c>
       <c r="D5" t="n">
-        <v>113.3427724552943</v>
+        <v>101.0709261522092</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.05418571684538</v>
+        <v>34.17365583712723</v>
       </c>
       <c r="C6" t="n">
-        <v>175.2959613317893</v>
+        <v>290.9389686581338</v>
       </c>
       <c r="D6" t="n">
-        <v>50.87809302488671</v>
+        <v>68.14605339488386</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.73990327829938</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="C7" t="n">
-        <v>169.7186526239631</v>
+        <v>320.2137034510694</v>
       </c>
       <c r="D7" t="n">
-        <v>33.11729530735765</v>
+        <v>44.79518424937346</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.43798264928109</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>143.8653085803276</v>
+        <v>189.511668089283</v>
       </c>
       <c r="D8" t="n">
-        <v>28.45595720759379</v>
+        <v>41.55738032076748</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>81.87186804795849</v>
+        <v>81.20624310447914</v>
       </c>
       <c r="D9" t="n">
-        <v>28.51093507903161</v>
+        <v>42.93280885441725</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
         <v>42.42131830050468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.421570675749381</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>31.98534020436108</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>33.58460721457913</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>26.25291535926396</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.95125677215293</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>41.33157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.439062207976577</v>
+        <v>0.9356055621472104</v>
       </c>
       <c r="C2" t="n">
-        <v>5.095270585040946</v>
+        <v>4.07523472032851</v>
       </c>
       <c r="D2" t="n">
-        <v>17.67538566725957</v>
+        <v>9.379617566374026</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.56823629877643</v>
+        <v>4.967643383488861</v>
       </c>
       <c r="C3" t="n">
-        <v>35.7503426501476</v>
+        <v>19.05572293943059</v>
       </c>
       <c r="D3" t="n">
-        <v>113.6176618124834</v>
+        <v>50.75144757103887</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.19952543480291</v>
+        <v>19.76945352041802</v>
       </c>
       <c r="C4" t="n">
-        <v>116.0131262108456</v>
+        <v>66.83836545282711</v>
       </c>
       <c r="D4" t="n">
-        <v>186.1059853032509</v>
+        <v>102.4080665253933</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.57825906446394</v>
+        <v>21.08303194870026</v>
       </c>
       <c r="C5" t="n">
-        <v>219.2242623583128</v>
+        <v>231.8151766652782</v>
       </c>
       <c r="D5" t="n">
-        <v>116.6316272645211</v>
+        <v>94.6650223819987</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.95731148929444</v>
+        <v>12.03524510636165</v>
       </c>
       <c r="C6" t="n">
-        <v>205.7262131726234</v>
+        <v>282.1641076775758</v>
       </c>
       <c r="D6" t="n">
-        <v>49.50953672516665</v>
+        <v>59.12968247908115</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="C7" t="n">
-        <v>179.8993763170025</v>
+        <v>133.2477071588984</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>35.75230614555609</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.253110981246429</v>
       </c>
       <c r="C8" t="n">
-        <v>101.2230970463674</v>
+        <v>59.83261383532185</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>31.62700229231099</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
         <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>30.95155987178918</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.19655482949439</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>26.33538216642069</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>22.56743447752142</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.53673825678252</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>13.78864650614645</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>35.1171153809084</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.587306111317845</v>
+        <v>0.4673119072214817</v>
       </c>
       <c r="C2" t="n">
-        <v>11.38532812615026</v>
+        <v>2.080323385298991</v>
       </c>
       <c r="D2" t="n">
-        <v>14.33940696822891</v>
+        <v>6.561019907481434</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.55012287174348</v>
+        <v>4.069344234103029</v>
       </c>
       <c r="C3" t="n">
-        <v>28.10743677258618</v>
+        <v>17.35239067256238</v>
       </c>
       <c r="D3" t="n">
-        <v>104.0210780034708</v>
+        <v>46.55447613538375</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>49.92776124717579</v>
+        <v>13.77097504747001</v>
       </c>
       <c r="C4" t="n">
-        <v>103.4035586974995</v>
+        <v>55.020086589104</v>
       </c>
       <c r="D4" t="n">
-        <v>196.1757715057104</v>
+        <v>100.0597260168349</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>60.74563920027141</v>
+        <v>20.07674055184728</v>
       </c>
       <c r="C5" t="n">
-        <v>218.389776809703</v>
+        <v>161.0557108816893</v>
       </c>
       <c r="D5" t="n">
-        <v>145.4950097693773</v>
+        <v>98.49383842856128</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.06047711369836</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="C6" t="n">
-        <v>266.5062135425434</v>
+        <v>269.4445844213541</v>
       </c>
       <c r="D6" t="n">
-        <v>66.53598715991909</v>
+        <v>61.26302024040947</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>4.012402867256713</v>
       </c>
       <c r="C7" t="n">
-        <v>230.3239019025272</v>
+        <v>183.0134800348734</v>
       </c>
       <c r="D7" t="n">
-        <v>37.72856427420492</v>
+        <v>34.01559445674349</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>1.168279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>152.9612010601743</v>
+        <v>70.18023463808323</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>26.95388322009618</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>63.34530712111692</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9964739198105126</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>18.50594422505238</v>
       </c>
       <c r="D10" t="n">
-        <v>24.05772749256809</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>13.50492141961912</v>
       </c>
       <c r="D11" t="n">
-        <v>23.45591614986479</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.70640068316797</v>
+        <v>11.49921085984289</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.56913593102267</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.065057390387548</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.565306751196915</v>
+        <v>0.2964878066825367</v>
       </c>
       <c r="C2" t="n">
-        <v>6.923284810348507</v>
+        <v>5.510549863937347</v>
       </c>
       <c r="D2" t="n">
-        <v>11.58854990092935</v>
+        <v>6.400013283984956</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.11047982669016</v>
+        <v>2.714532402242431</v>
       </c>
       <c r="C3" t="n">
-        <v>35.58344554042564</v>
+        <v>11.73679380427062</v>
       </c>
       <c r="D3" t="n">
-        <v>94.90555056953917</v>
+        <v>40.9977841293468</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.52462279362884</v>
+        <v>10.771735810996</v>
       </c>
       <c r="C4" t="n">
-        <v>92.87431456945251</v>
+        <v>48.79187915336223</v>
       </c>
       <c r="D4" t="n">
-        <v>203.2463184716959</v>
+        <v>101.042455468786</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>66.8570186592078</v>
+        <v>20.7148765596077</v>
       </c>
       <c r="C5" t="n">
-        <v>213.7510189071369</v>
+        <v>127.9953569411779</v>
       </c>
       <c r="D5" t="n">
-        <v>164.7127210800086</v>
+        <v>112.6310053697153</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>54.86300695642451</v>
+        <v>19.76356303419254</v>
       </c>
       <c r="C6" t="n">
-        <v>303.4169819791107</v>
+        <v>266.3049552631728</v>
       </c>
       <c r="D6" t="n">
-        <v>80.26180181299375</v>
+        <v>77.72594749292425</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.32530264747096</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>281.8263864673148</v>
+        <v>293.5641620192897</v>
       </c>
       <c r="D7" t="n">
-        <v>42.69915290080652</v>
+        <v>43.17824578047897</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>2.503456645829366</v>
       </c>
       <c r="C8" t="n">
-        <v>191.0137420767806</v>
+        <v>157.0501802483622</v>
       </c>
       <c r="D8" t="n">
-        <v>31.79389940203295</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.6656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>67.11718180083317</v>
+        <v>59.46249495082079</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>23.51874800293658</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.2847068342315751</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>20.78359889890498</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>21.67895280517806</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>23.63361248433346</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>13.23494080095125</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.244496236086461</v>
+        <v>0.5959208564778139</v>
       </c>
       <c r="C2" t="n">
-        <v>7.126506585127596</v>
+        <v>12.48783079801943</v>
       </c>
       <c r="D2" t="n">
-        <v>16.50317890838888</v>
+        <v>11.74170254279185</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.68418033886879</v>
+        <v>1.801507037292897</v>
       </c>
       <c r="C3" t="n">
-        <v>31.50428382928014</v>
+        <v>17.0824100538945</v>
       </c>
       <c r="D3" t="n">
-        <v>84.84263660100936</v>
+        <v>36.87935251003143</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.53065214857457</v>
+        <v>7.9256492163845</v>
       </c>
       <c r="C4" t="n">
-        <v>90.79399118415351</v>
+        <v>38.30092318578082</v>
       </c>
       <c r="D4" t="n">
-        <v>202.9144877476605</v>
+        <v>97.9538771912255</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>67.59332943739291</v>
+        <v>18.87409961414493</v>
       </c>
       <c r="C5" t="n">
-        <v>196.1286476159066</v>
+        <v>108.262228085817</v>
       </c>
       <c r="D5" t="n">
-        <v>187.9065105928395</v>
+        <v>123.3075116533994</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.85170901005907</v>
+        <v>23.98998690097506</v>
       </c>
       <c r="C6" t="n">
-        <v>317.7868231261713</v>
+        <v>236.4382266045764</v>
       </c>
       <c r="D6" t="n">
-        <v>100.3071264383051</v>
+        <v>94.10837143369076</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>32.63820242768521</v>
+        <v>15.81006502919063</v>
       </c>
       <c r="C7" t="n">
-        <v>339.8565115176395</v>
+        <v>341.7129964263703</v>
       </c>
       <c r="D7" t="n">
-        <v>51.26293812495145</v>
+        <v>53.65840252331367</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>258.0229316301467</v>
+        <v>270.5402148592935</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.442187377538564</v>
       </c>
       <c r="C9" t="n">
-        <v>121.9203021472986</v>
+        <v>123.8062394871567</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>25.62656032395449</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>45.83780031128358</v>
+        <v>47.26133448244146</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>21.78007281871549</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>12.48783079801943</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>8.600109889202059</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.596583809012571</v>
+        <v>4.627958677819464</v>
       </c>
       <c r="C2" t="n">
-        <v>9.591675070491338</v>
+        <v>6.603235058764047</v>
       </c>
       <c r="D2" t="n">
-        <v>13.03171902617216</v>
+        <v>7.621307428067988</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.87201294554942</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C2" t="n">
-        <v>4.275511251994859</v>
+        <v>8.731664081571131</v>
       </c>
       <c r="D2" t="n">
-        <v>12.27871853701486</v>
+        <v>10.77958979262998</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.53401399784803</v>
+        <v>1.880046853632642</v>
       </c>
       <c r="C3" t="n">
-        <v>35.92214849839079</v>
+        <v>32.83946070705581</v>
       </c>
       <c r="D3" t="n">
-        <v>92.06339096574465</v>
+        <v>37.36531762363361</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>52.17399999449249</v>
+        <v>5.743224069843841</v>
       </c>
       <c r="C4" t="n">
-        <v>126.1594887342364</v>
+        <v>40.36848385092459</v>
       </c>
       <c r="D4" t="n">
-        <v>203.5909119158866</v>
+        <v>94.63556995087129</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.08551952792327</v>
+        <v>15.85522542358599</v>
       </c>
       <c r="C5" t="n">
-        <v>278.1045809205153</v>
+        <v>89.33904108645976</v>
       </c>
       <c r="D5" t="n">
-        <v>164.050041379642</v>
+        <v>129.5416095753667</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.24658290468198</v>
+        <v>25.03652995370216</v>
       </c>
       <c r="C6" t="n">
-        <v>276.7703857904439</v>
+        <v>208.1413125250706</v>
       </c>
       <c r="D6" t="n">
-        <v>77.8467024605466</v>
+        <v>107.5121728397725</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.868887775987432</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="C7" t="n">
-        <v>181.456428175938</v>
+        <v>345.9050591235041</v>
       </c>
       <c r="D7" t="n">
-        <v>30.18285141936394</v>
+        <v>65.75549773504287</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>89.87409358527424</v>
+        <v>352.4032471779138</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2218749811597791</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>34.94530953266521</v>
+        <v>218.4359189518025</v>
       </c>
       <c r="D9" t="n">
-        <v>19.41406085148067</v>
+        <v>28.06718511671205</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>20.35653864755762</v>
+        <v>89.82500620006192</v>
       </c>
       <c r="D10" t="n">
-        <v>18.64829764216817</v>
+        <v>22.63419332141022</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>14.39340309196248</v>
+        <v>36.25005223160922</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>19.54659679155399</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.19741340401162</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>10.14636252339079</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>11.46681318560274</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.08861933528947</v>
+        <v>5.883613991551134</v>
       </c>
       <c r="C2" t="n">
-        <v>10.20035864712436</v>
+        <v>10.88660029239288</v>
       </c>
       <c r="D2" t="n">
-        <v>10.6333093846972</v>
+        <v>16.4511462800638</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.37126486312131</v>
+        <v>7.642905877561418</v>
       </c>
       <c r="C3" t="n">
-        <v>24.17062847855647</v>
+        <v>13.03760951239764</v>
       </c>
       <c r="D3" t="n">
-        <v>14.08317081742049</v>
+        <v>8.251589454194441</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.845546815263761</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.60468413702056</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39647365410934</v>
+        <v>11.67853784032893</v>
       </c>
       <c r="C21" t="n">
-        <v>70.13447971857242</v>
+        <v>59.94982758035518</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576055724012863</v>
+        <v>0.7785691893552621</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.244496236086461</v>
+        <v>3.392920065876976</v>
       </c>
       <c r="C2" t="n">
-        <v>6.977280934082081</v>
+        <v>5.737333583618359</v>
       </c>
       <c r="D2" t="n">
-        <v>17.54481322259475</v>
+        <v>14.62607729786898</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.00511402716626</v>
+        <v>15.70305452942773</v>
       </c>
       <c r="C3" t="n">
-        <v>33.934109397291</v>
+        <v>32.68238107437632</v>
       </c>
       <c r="D3" t="n">
-        <v>19.61041039233004</v>
+        <v>20.65106295883166</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.44511692511808</v>
+        <v>9.508226515630358</v>
       </c>
       <c r="C4" t="n">
-        <v>37.3820073346058</v>
+        <v>21.74767514447534</v>
       </c>
       <c r="D4" t="n">
-        <v>22.44962475301181</v>
+        <v>18.51870694520758</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.3139636433765</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.60312155223957</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>49.68134257340984</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43598738588758</v>
+        <v>13.63017727038768</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11656120547811</v>
+        <v>73.76331228680391</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249681554923702</v>
+        <v>1.603550267104433</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.178138302825178</v>
+        <v>2.272745935331366</v>
       </c>
       <c r="C2" t="n">
-        <v>6.46971737098648</v>
+        <v>3.105267988532661</v>
       </c>
       <c r="D2" t="n">
-        <v>29.27768003604838</v>
+        <v>14.95888976960865</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.1468455494763</v>
+        <v>13.47448724078747</v>
       </c>
       <c r="C3" t="n">
-        <v>29.86476516318797</v>
+        <v>26.37956081311179</v>
       </c>
       <c r="D3" t="n">
-        <v>29.09409321535422</v>
+        <v>27.94544840138546</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.16504109196725</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="C4" t="n">
-        <v>64.91119470939061</v>
+        <v>58.9254789565978</v>
       </c>
       <c r="D4" t="n">
-        <v>27.23564481121501</v>
+        <v>25.04045694451915</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.61041039233004</v>
+        <v>8.933904108645976</v>
       </c>
       <c r="C5" t="n">
-        <v>41.01251034491051</v>
+        <v>26.11448893296516</v>
       </c>
       <c r="D5" t="n">
-        <v>30.99868376159304</v>
+        <v>26.4090132442392</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>10.50568218314512</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.70768553050848</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.07343545583603</v>
       </c>
       <c r="D9" t="n">
-        <v>41.49062147687869</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>48.9695754878309</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.57727731675966</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72231519675395</v>
+        <v>14.84207520339255</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0061227001991</v>
+        <v>87.40333175331168</v>
       </c>
       <c r="D21" t="n">
-        <v>4.180578799188488</v>
+        <v>2.473679200565425</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.284167054883833</v>
+        <v>2.414117604742907</v>
       </c>
       <c r="C2" t="n">
-        <v>5.154175447295755</v>
+        <v>12.30424397732527</v>
       </c>
       <c r="D2" t="n">
-        <v>32.06388002070083</v>
+        <v>22.09325033637022</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.09284942574272</v>
+        <v>10.28380720198534</v>
       </c>
       <c r="C3" t="n">
-        <v>27.13059780686061</v>
+        <v>17.57819264453914</v>
       </c>
       <c r="D3" t="n">
-        <v>44.87077882260047</v>
+        <v>33.4285093296039</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.27088991757666</v>
+        <v>24.72138894063893</v>
       </c>
       <c r="C4" t="n">
-        <v>70.28429989473339</v>
+        <v>63.2520410892135</v>
       </c>
       <c r="D4" t="n">
-        <v>35.22510762837556</v>
+        <v>33.17030968338698</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.11006322052944</v>
+        <v>21.84388641949153</v>
       </c>
       <c r="C5" t="n">
-        <v>82.39317607891357</v>
+        <v>74.12195167063419</v>
       </c>
       <c r="D5" t="n">
-        <v>33.74757733348411</v>
+        <v>29.77149913128453</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.97990738202533</v>
+        <v>8.493099389439159</v>
       </c>
       <c r="C6" t="n">
-        <v>39.56737772425921</v>
+        <v>27.73339089726815</v>
       </c>
       <c r="D6" t="n">
-        <v>37.63529824230149</v>
+        <v>33.73088762251191</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>17.6066633279623</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.927612711792993</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.876561831172157</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>27.84531013555227</v>
       </c>
       <c r="D9" t="n">
-        <v>42.3781214015178</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.54251523648354</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.6434553235717</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.51560713784138</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.26838664282043</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.03461847886948</v>
+        <v>16.08744323750253</v>
       </c>
       <c r="C21" t="n">
-        <v>117.65441579072</v>
+        <v>101.6049046579107</v>
       </c>
       <c r="D21" t="n">
-        <v>6.011539492956493</v>
+        <v>3.386830155263691</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.63308840051895</v>
+        <v>1.714131491614931</v>
       </c>
       <c r="C2" t="n">
-        <v>5.789366211943441</v>
+        <v>9.280461048245099</v>
       </c>
       <c r="D2" t="n">
-        <v>44.2463872826995</v>
+        <v>21.23618459056275</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.88882582970863</v>
+        <v>9.179341034707678</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71135047941821</v>
+        <v>35.47545329295849</v>
       </c>
       <c r="D3" t="n">
-        <v>54.87478792887547</v>
+        <v>42.78456495107599</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.08623923372025</v>
+        <v>22.2837093909941</v>
       </c>
       <c r="C4" t="n">
-        <v>56.99830821316132</v>
+        <v>51.8932201510779</v>
       </c>
       <c r="D4" t="n">
-        <v>41.73409490753191</v>
+        <v>41.64475586644545</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.08427573831176</v>
+        <v>29.52606220522283</v>
       </c>
       <c r="C5" t="n">
-        <v>79.66882619962867</v>
+        <v>97.65935287995148</v>
       </c>
       <c r="D5" t="n">
-        <v>31.24412068765475</v>
+        <v>35.04839304161113</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.75098024048658</v>
+        <v>19.07928488433252</v>
       </c>
       <c r="C6" t="n">
-        <v>57.47936458824226</v>
+        <v>75.14984151698062</v>
       </c>
       <c r="D6" t="n">
-        <v>30.51075515258238</v>
+        <v>35.86422538384024</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.827073535332318</v>
+        <v>8.384125394267761</v>
       </c>
       <c r="C7" t="n">
-        <v>25.03260296288517</v>
+        <v>29.40432548989622</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.50780990946962</v>
       </c>
       <c r="D9" t="n">
-        <v>30.28593492830985</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>33.02599277086271</v>
+        <v>43.70249905454677</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.24313893995049</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>44.47807974090174</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>41.88626580169016</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.042108848184713</v>
+        <v>17.3582216788619</v>
       </c>
       <c r="C21" t="n">
-        <v>66.01977045173169</v>
+        <v>115.4321741644317</v>
       </c>
       <c r="D21" t="n">
-        <v>4.401318030115446</v>
+        <v>4.339555419715476</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.724971774090651</v>
+        <v>3.201479263548849</v>
       </c>
       <c r="C2" t="n">
-        <v>8.301658587111028</v>
+        <v>12.14814609235003</v>
       </c>
       <c r="D2" t="n">
-        <v>39.02447124381072</v>
+        <v>22.73236809183489</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.4539526544563</v>
+        <v>7.392560212978482</v>
       </c>
       <c r="C3" t="n">
-        <v>22.25131171675396</v>
+        <v>35.67671157232909</v>
       </c>
       <c r="D3" t="n">
-        <v>78.78034452728531</v>
+        <v>48.9695754878309</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.71910665006095</v>
+        <v>19.75669080026281</v>
       </c>
       <c r="C4" t="n">
-        <v>54.94351026817274</v>
+        <v>71.3308429474605</v>
       </c>
       <c r="D4" t="n">
-        <v>60.81436153956867</v>
+        <v>52.40372895728624</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.79728661350221</v>
+        <v>31.78408192499049</v>
       </c>
       <c r="C5" t="n">
-        <v>95.25407100454679</v>
+        <v>95.72040116406403</v>
       </c>
       <c r="D5" t="n">
-        <v>39.39262663290327</v>
+        <v>40.98796665230434</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.98748362621883</v>
+        <v>28.90068891761761</v>
       </c>
       <c r="C6" t="n">
-        <v>97.52976218299091</v>
+        <v>115.1599874558551</v>
       </c>
       <c r="D6" t="n">
-        <v>34.05290086950487</v>
+        <v>38.88309957439917</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.67221943996858</v>
+        <v>15.27108553955913</v>
       </c>
       <c r="C7" t="n">
-        <v>58.20978488020188</v>
+        <v>68.15096213340507</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41672835715293</v>
+        <v>38.5669768136317</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>8.595201150680824</v>
       </c>
       <c r="C8" t="n">
-        <v>27.12078032981814</v>
+        <v>31.96079651175491</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.431249284071605</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.72812230584841</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.82655911818034</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.256498192715677</v>
       </c>
       <c r="C10" t="n">
-        <v>24.20008090968388</v>
+        <v>34.44952694202058</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>43.56014563743098</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>47.08952863419825</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>33.1958351236974</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.256468312021784</v>
+        <v>18.64863249859151</v>
       </c>
       <c r="C21" t="n">
-        <v>75.28585873722602</v>
+        <v>128.7643672521795</v>
       </c>
       <c r="D21" t="n">
-        <v>5.442351234016338</v>
+        <v>5.32818071388329</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.695519342963247</v>
+        <v>2.799944452511903</v>
       </c>
       <c r="C2" t="n">
-        <v>12.51433798603409</v>
+        <v>7.482881001769189</v>
       </c>
       <c r="D2" t="n">
-        <v>36.20587358491812</v>
+        <v>17.82755656141783</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.23305942100077</v>
+        <v>11.57480543306989</v>
       </c>
       <c r="C3" t="n">
-        <v>28.11234551110741</v>
+        <v>54.64407721837746</v>
       </c>
       <c r="D3" t="n">
-        <v>90.91474615177589</v>
+        <v>54.40845776935824</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.9217886454923</v>
+        <v>15.26421330562941</v>
       </c>
       <c r="C4" t="n">
-        <v>55.39020547360504</v>
+        <v>92.28722944231292</v>
       </c>
       <c r="D4" t="n">
-        <v>84.64236006934301</v>
+        <v>49.82565948593412</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.96404485450392</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="C5" t="n">
-        <v>98.76381904722915</v>
+        <v>68.79597037509525</v>
       </c>
       <c r="D5" t="n">
-        <v>52.327152636355</v>
+        <v>35.41654843070369</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.97618567985338</v>
+        <v>9.45913913041802</v>
       </c>
       <c r="C6" t="n">
-        <v>125.3436563920073</v>
+        <v>44.88059629964295</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>25.39879485656924</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.69135567243478</v>
+        <v>5.689227946110266</v>
       </c>
       <c r="C7" t="n">
-        <v>102.4659896399438</v>
+        <v>22.45747873464579</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.26555490623215</v>
+        <v>5.841398840268521</v>
       </c>
       <c r="C8" t="n">
-        <v>53.49052366588747</v>
+        <v>23.36559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>33.37942194439155</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>29.17656002251095</v>
+        <v>26.29218526743382</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.62008900065227</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>36.86953503298896</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.00617789032851</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>34.86186097780424</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>34.10886048864694</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.456356709960037</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>83.88401298705041</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.524312121215032</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
